--- a/tests/fixtures/fhfa_hpi/hpi_at_county.xlsx
+++ b/tests/fixtures/fhfa_hpi/hpi_at_county.xlsx
@@ -6493,7 +6493,7 @@
   <sheetPr>
     <tabColor indexed="41"/>
   </sheetPr>
-  <dimension ref="A1:H308"/>
+  <dimension ref="A1:H106258"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
@@ -7628,6583 +7628,6583 @@
       </c>
     </row>
     <row r="1937" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="5" t="s">
+      <c r="A1937" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B1937" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C1937" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D1937" s="5">
         <v>1979</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F1937" s="7">
         <v>100</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G1937" s="7">
         <v>69.08</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H1937" s="7">
         <v>41.63</v>
       </c>
     </row>
     <row r="1938" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
+      <c r="A1938" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B1938" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C1938" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D1938" s="5">
         <v>1980</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E1938" s="7">
         <v>9.16</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F1938" s="7">
         <v>109.16</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G1938" s="7">
         <v>75.41</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H1938" s="7">
         <v>45.44</v>
       </c>
     </row>
     <row r="1939" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="5" t="s">
+      <c r="A1939" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B1939" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C1939" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D1939" s="5">
         <v>1981</v>
       </c>
     </row>
     <row r="1940" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
+      <c r="A1940" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B1940" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C1940" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D1940" s="5">
         <v>1982</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F1940" s="7">
         <v>114.53</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G1940" s="7">
         <v>79.12</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H1940" s="7">
         <v>47.68</v>
       </c>
     </row>
     <row r="1941" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="5" t="s">
+      <c r="A1941" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B1941" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C1941" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D1941" s="5">
         <v>1983</v>
       </c>
     </row>
     <row r="1942" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
+      <c r="A1942" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B1942" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C1942" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D1942" s="5">
         <v>1984</v>
       </c>
     </row>
     <row r="1943" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="5" t="s">
+      <c r="A1943" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B1943" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C1943" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D1943" s="5">
         <v>1985</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F1943" s="7">
         <v>130.57</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G1943" s="7">
         <v>90.2</v>
       </c>
-      <c r="H53" s="7">
+      <c r="H1943" s="7">
         <v>54.36</v>
       </c>
     </row>
     <row r="1944" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" s="5" t="s">
+      <c r="A1944" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B1944" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C1944" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D1944" s="5">
         <v>1986</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E1944" s="7">
         <v>6.22</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F1944" s="7">
         <v>138.69999999999999</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G1944" s="7">
         <v>95.81</v>
       </c>
-      <c r="H54" s="7">
+      <c r="H1944" s="7">
         <v>57.74</v>
       </c>
     </row>
     <row r="1945" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="5" t="s">
+      <c r="A1945" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B1945" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C1945" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D1945" s="5">
         <v>1987</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E1945" s="7">
         <v>-1.93</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F1945" s="7">
         <v>136.02000000000001</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G1945" s="7">
         <v>93.96</v>
       </c>
-      <c r="H55" s="7">
+      <c r="H1945" s="7">
         <v>56.63</v>
       </c>
     </row>
     <row r="1946" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
+      <c r="A1946" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B1946" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C1946" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D1946" s="5">
         <v>1988</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E1946" s="7">
         <v>3.42</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F1946" s="7">
         <v>140.66999999999999</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G1946" s="7">
         <v>97.18</v>
       </c>
-      <c r="H56" s="7">
+      <c r="H1946" s="7">
         <v>58.57</v>
       </c>
     </row>
     <row r="1947" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="5" t="s">
+      <c r="A1947" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B1947" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C1947" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D1947" s="5">
         <v>1989</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E1947" s="7">
         <v>1.63</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F1947" s="7">
         <v>142.97</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G1947" s="7">
         <v>98.76</v>
       </c>
-      <c r="H57" s="7">
+      <c r="H1947" s="7">
         <v>59.52</v>
       </c>
     </row>
     <row r="1948" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
+      <c r="A1948" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B1948" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C1948" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D1948" s="5">
         <v>1990</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E1948" s="7">
         <v>1.25</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F1948" s="7">
         <v>144.76</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G1948" s="7">
         <v>100</v>
       </c>
-      <c r="H58" s="7">
+      <c r="H1948" s="7">
         <v>60.27</v>
       </c>
     </row>
     <row r="1949" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="5" t="s">
+      <c r="A1949" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B1949" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C1949" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D1949" s="5">
         <v>1991</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E1949" s="7">
         <v>9.0399999999999991</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F1949" s="7">
         <v>157.84</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G1949" s="7">
         <v>109.04</v>
       </c>
-      <c r="H59" s="7">
+      <c r="H1949" s="7">
         <v>65.709999999999994</v>
       </c>
     </row>
     <row r="1950" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="5" t="s">
+      <c r="A1950" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B1950" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C1950" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D1950" s="5">
         <v>1992</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E1950" s="7">
         <v>5.51</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F1950" s="7">
         <v>166.54</v>
       </c>
-      <c r="G60" s="7">
+      <c r="G1950" s="7">
         <v>115.05</v>
       </c>
-      <c r="H60" s="7">
+      <c r="H1950" s="7">
         <v>69.34</v>
       </c>
     </row>
     <row r="1951" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="5" t="s">
+      <c r="A1951" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B1951" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C61" s="13" t="s">
+      <c r="C1951" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D1951" s="5">
         <v>1993</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E1951" s="7">
         <v>2.33</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F1951" s="7">
         <v>170.42</v>
       </c>
-      <c r="G61" s="7">
+      <c r="G1951" s="7">
         <v>117.73</v>
       </c>
-      <c r="H61" s="7">
+      <c r="H1951" s="7">
         <v>70.95</v>
       </c>
     </row>
     <row r="1952" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="5" t="s">
+      <c r="A1952" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B1952" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C1952" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D1952" s="5">
         <v>1994</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E1952" s="7">
         <v>6.83</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F1952" s="7">
         <v>182.06</v>
       </c>
-      <c r="G62" s="7">
+      <c r="G1952" s="7">
         <v>125.77</v>
       </c>
-      <c r="H62" s="7">
+      <c r="H1952" s="7">
         <v>75.8</v>
       </c>
     </row>
     <row r="1953" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="5" t="s">
+      <c r="A1953" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B1953" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C1953" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D1953" s="5">
         <v>1995</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E1953" s="7">
         <v>5.5</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F1953" s="7">
         <v>192.07</v>
       </c>
-      <c r="G63" s="7">
+      <c r="G1953" s="7">
         <v>132.68</v>
       </c>
-      <c r="H63" s="7">
+      <c r="H1953" s="7">
         <v>79.959999999999994</v>
       </c>
     </row>
     <row r="1954" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="5" t="s">
+      <c r="A1954" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B1954" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C1954" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D1954" s="5">
         <v>1996</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E1954" s="7">
         <v>5.29</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F1954" s="7">
         <v>202.23</v>
       </c>
-      <c r="G64" s="7">
+      <c r="G1954" s="7">
         <v>139.69999999999999</v>
       </c>
-      <c r="H64" s="7">
+      <c r="H1954" s="7">
         <v>84.19</v>
       </c>
     </row>
     <row r="1955" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="5" t="s">
+      <c r="A1955" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B1955" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C1955" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D1955" s="5">
         <v>1997</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E1955" s="7">
         <v>6.23</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F1955" s="7">
         <v>214.82</v>
       </c>
-      <c r="G65" s="7">
+      <c r="G1955" s="7">
         <v>148.4</v>
       </c>
-      <c r="H65" s="7">
+      <c r="H1955" s="7">
         <v>89.44</v>
       </c>
     </row>
     <row r="1956" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="5" t="s">
+      <c r="A1956" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B1956" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C1956" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D1956" s="5">
         <v>1998</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E1956" s="7">
         <v>4.5</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F1956" s="7">
         <v>224.49</v>
       </c>
-      <c r="G66" s="7">
+      <c r="G1956" s="7">
         <v>155.08000000000001</v>
       </c>
-      <c r="H66" s="7">
+      <c r="H1956" s="7">
         <v>93.46</v>
       </c>
     </row>
     <row r="1957" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="5" t="s">
+      <c r="A1957" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B1957" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C1957" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D1957" s="5">
         <v>1999</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E1957" s="7">
         <v>2.86</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F1957" s="7">
         <v>230.92</v>
       </c>
-      <c r="G67" s="7">
+      <c r="G1957" s="7">
         <v>159.52000000000001</v>
       </c>
-      <c r="H67" s="7">
+      <c r="H1957" s="7">
         <v>96.14</v>
       </c>
     </row>
     <row r="1958" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="5" t="s">
+      <c r="A1958" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B1958" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C1958" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D1958" s="5">
         <v>2000</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E1958" s="7">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F1958" s="7">
         <v>240.2</v>
       </c>
-      <c r="G68" s="7">
+      <c r="G1958" s="7">
         <v>165.93</v>
       </c>
-      <c r="H68" s="7">
+      <c r="H1958" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="1959" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="5" t="s">
+      <c r="A1959" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B1959" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C1959" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D1959" s="5">
         <v>2001</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E1959" s="7">
         <v>4.91</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F1959" s="7">
         <v>252</v>
       </c>
-      <c r="G69" s="7">
+      <c r="G1959" s="7">
         <v>174.08</v>
       </c>
-      <c r="H69" s="7">
+      <c r="H1959" s="7">
         <v>104.91</v>
       </c>
     </row>
     <row r="1960" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="5" t="s">
+      <c r="A1960" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B1960" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C1960" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D1960" s="5">
         <v>2002</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E1960" s="7">
         <v>2.48</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F1960" s="7">
         <v>258.26</v>
       </c>
-      <c r="G70" s="7">
+      <c r="G1960" s="7">
         <v>178.41</v>
       </c>
-      <c r="H70" s="7">
+      <c r="H1960" s="7">
         <v>107.52</v>
       </c>
     </row>
     <row r="1961" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="5" t="s">
+      <c r="A1961" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B1961" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C1961" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D1961" s="5">
         <v>2003</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E1961" s="7">
         <v>3.04</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F1961" s="7">
         <v>266.10000000000002</v>
       </c>
-      <c r="G71" s="7">
+      <c r="G1961" s="7">
         <v>183.83</v>
       </c>
-      <c r="H71" s="7">
+      <c r="H1961" s="7">
         <v>110.79</v>
       </c>
     </row>
     <row r="1962" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="5" t="s">
+      <c r="A1962" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B1962" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C1962" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D1962" s="5">
         <v>2004</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E1962" s="7">
         <v>3.02</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F1962" s="7">
         <v>274.14999999999998</v>
       </c>
-      <c r="G72" s="7">
+      <c r="G1962" s="7">
         <v>189.39</v>
       </c>
-      <c r="H72" s="7">
+      <c r="H1962" s="7">
         <v>114.14</v>
       </c>
     </row>
     <row r="1963" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="5" t="s">
+      <c r="A1963" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B1963" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C1963" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D1963" s="5">
         <v>2005</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E1963" s="7">
         <v>6.02</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F1963" s="7">
         <v>290.64999999999998</v>
       </c>
-      <c r="G73" s="7">
+      <c r="G1963" s="7">
         <v>200.79</v>
       </c>
-      <c r="H73" s="7">
+      <c r="H1963" s="7">
         <v>121.01</v>
       </c>
     </row>
     <row r="1964" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="5" t="s">
+      <c r="A1964" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B1964" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C74" s="13" t="s">
+      <c r="C1964" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D1964" s="5">
         <v>2006</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E1964" s="7">
         <v>6.71</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F1964" s="7">
         <v>310.14</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G1964" s="7">
         <v>214.25</v>
       </c>
-      <c r="H74" s="7">
+      <c r="H1964" s="7">
         <v>129.12</v>
       </c>
     </row>
     <row r="1965" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="5" t="s">
+      <c r="A1965" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B1965" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C1965" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D1965" s="5">
         <v>2007</v>
       </c>
-      <c r="E75" s="7">
+      <c r="E1965" s="7">
         <v>2.84</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F1965" s="7">
         <v>318.95</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G1965" s="7">
         <v>220.33</v>
       </c>
-      <c r="H75" s="7">
+      <c r="H1965" s="7">
         <v>132.79</v>
       </c>
     </row>
     <row r="1966" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="5" t="s">
+      <c r="A1966" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B1966" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C1966" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D1966" s="5">
         <v>2008</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E1966" s="7">
         <v>0.51</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F1966" s="7">
         <v>320.57</v>
       </c>
-      <c r="G76" s="7">
+      <c r="G1966" s="7">
         <v>221.45</v>
       </c>
-      <c r="H76" s="7">
+      <c r="H1966" s="7">
         <v>133.46</v>
       </c>
     </row>
     <row r="1967" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="5" t="s">
+      <c r="A1967" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B1967" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C1967" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D1967" s="5">
         <v>2009</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E1967" s="7">
         <v>-2.82</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F1967" s="7">
         <v>311.52999999999997</v>
       </c>
-      <c r="G77" s="7">
+      <c r="G1967" s="7">
         <v>215.21</v>
       </c>
-      <c r="H77" s="7">
+      <c r="H1967" s="7">
         <v>129.69999999999999</v>
       </c>
     </row>
     <row r="1968" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="5" t="s">
+      <c r="A1968" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B1968" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C1968" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D1968" s="5">
         <v>2010</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E1968" s="7">
         <v>-4.88</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F1968" s="7">
         <v>296.32</v>
       </c>
-      <c r="G78" s="7">
+      <c r="G1968" s="7">
         <v>204.7</v>
       </c>
-      <c r="H78" s="7">
+      <c r="H1968" s="7">
         <v>123.36</v>
       </c>
     </row>
     <row r="1969" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="5" t="s">
+      <c r="A1969" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B1969" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C1969" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D1969" s="5">
         <v>2011</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E1969" s="7">
         <v>-3.36</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F1969" s="7">
         <v>286.37</v>
       </c>
-      <c r="G79" s="7">
+      <c r="G1969" s="7">
         <v>197.82</v>
       </c>
-      <c r="H79" s="7">
+      <c r="H1969" s="7">
         <v>119.22</v>
       </c>
     </row>
     <row r="1970" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="5" t="s">
+      <c r="A1970" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B1970" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C1970" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D1970" s="5">
         <v>2012</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E1970" s="7">
         <v>-1.1299999999999999</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F1970" s="7">
         <v>283.13</v>
       </c>
-      <c r="G80" s="7">
+      <c r="G1970" s="7">
         <v>195.59</v>
       </c>
-      <c r="H80" s="7">
+      <c r="H1970" s="7">
         <v>117.87</v>
       </c>
     </row>
     <row r="1971" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="5" t="s">
+      <c r="A1971" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B1971" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C1971" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D1971" s="5">
         <v>2013</v>
       </c>
-      <c r="E81" s="7">
+      <c r="E1971" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F1971" s="7">
         <v>283.33</v>
       </c>
-      <c r="G81" s="7">
+      <c r="G1971" s="7">
         <v>195.72</v>
       </c>
-      <c r="H81" s="7">
+      <c r="H1971" s="7">
         <v>117.96</v>
       </c>
     </row>
     <row r="1972" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="5" t="s">
+      <c r="A1972" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B1972" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C1972" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D1972" s="5">
         <v>2014</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E1972" s="7">
         <v>1.33</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F1972" s="7">
         <v>287.08999999999997</v>
       </c>
-      <c r="G82" s="7">
+      <c r="G1972" s="7">
         <v>198.32</v>
       </c>
-      <c r="H82" s="7">
+      <c r="H1972" s="7">
         <v>119.52</v>
       </c>
     </row>
     <row r="1973" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="5" t="s">
+      <c r="A1973" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B1973" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C1973" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D1973" s="5">
         <v>2015</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E1973" s="7">
         <v>5.05</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F1973" s="7">
         <v>301.58</v>
       </c>
-      <c r="G83" s="7">
+      <c r="G1973" s="7">
         <v>208.33</v>
       </c>
-      <c r="H83" s="7">
+      <c r="H1973" s="7">
         <v>125.56</v>
       </c>
     </row>
     <row r="1974" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="5" t="s">
+      <c r="A1974" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B1974" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C1974" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D1974" s="5">
         <v>2016</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E1974" s="7">
         <v>1.52</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F1974" s="7">
         <v>306.14999999999998</v>
       </c>
-      <c r="G84" s="7">
+      <c r="G1974" s="7">
         <v>211.49</v>
       </c>
-      <c r="H84" s="7">
+      <c r="H1974" s="7">
         <v>127.46</v>
       </c>
     </row>
     <row r="1975" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="5" t="s">
+      <c r="A1975" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="B1975" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C1975" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D1975" s="5">
         <v>2017</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E1975" s="7">
         <v>2.7</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F1975" s="7">
         <v>314.42</v>
       </c>
-      <c r="G85" s="7">
+      <c r="G1975" s="7">
         <v>217.2</v>
       </c>
-      <c r="H85" s="7">
+      <c r="H1975" s="7">
         <v>130.9</v>
       </c>
     </row>
     <row r="1976" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="5" t="s">
+      <c r="A1976" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B1976" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C1976" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D1976" s="5">
         <v>2018</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E1976" s="7">
         <v>6.42</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F1976" s="7">
         <v>334.62</v>
       </c>
-      <c r="G86" s="7">
+      <c r="G1976" s="7">
         <v>231.16</v>
       </c>
-      <c r="H86" s="7">
+      <c r="H1976" s="7">
         <v>139.31</v>
       </c>
     </row>
     <row r="1977" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="5" t="s">
+      <c r="A1977" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B1977" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C1977" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D1977" s="5">
         <v>2019</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E1977" s="7">
         <v>3.26</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F1977" s="7">
         <v>345.52</v>
       </c>
-      <c r="G87" s="7">
+      <c r="G1977" s="7">
         <v>238.69</v>
       </c>
-      <c r="H87" s="7">
+      <c r="H1977" s="7">
         <v>143.85</v>
       </c>
     </row>
     <row r="1978" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="5" t="s">
+      <c r="A1978" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B1978" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C1978" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D1978" s="5">
         <v>2020</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E1978" s="7">
         <v>3.97</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F1978" s="7">
         <v>359.25</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G1978" s="7">
         <v>248.17</v>
       </c>
-      <c r="H88" s="7">
+      <c r="H1978" s="7">
         <v>149.56</v>
       </c>
     </row>
     <row r="1979" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="5" t="s">
+      <c r="A1979" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B1979" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C1979" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D1979" s="5">
         <v>2021</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E1979" s="7">
         <v>9.8699999999999992</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F1979" s="7">
         <v>394.72</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G1979" s="7">
         <v>272.68</v>
       </c>
-      <c r="H89" s="7">
+      <c r="H1979" s="7">
         <v>164.33</v>
       </c>
     </row>
     <row r="1980" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="5" t="s">
+      <c r="A1980" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B1980" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C1980" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D1980" s="5">
         <v>2022</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E1980" s="7">
         <v>14.93</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F1980" s="7">
         <v>453.68</v>
       </c>
-      <c r="G90" s="7">
+      <c r="G1980" s="7">
         <v>313.39999999999998</v>
       </c>
-      <c r="H90" s="7">
+      <c r="H1980" s="7">
         <v>188.88</v>
       </c>
     </row>
     <row r="1981" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="5" t="s">
+      <c r="A1981" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B1981" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C1981" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D1981" s="5">
         <v>2023</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E1981" s="7">
         <v>5.58</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F1981" s="7">
         <v>478.99</v>
       </c>
-      <c r="G91" s="7">
+      <c r="G1981" s="7">
         <v>330.89</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H1981" s="7">
         <v>199.42</v>
       </c>
     </row>
     <row r="1982" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="5" t="s">
+      <c r="A1982" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B1982" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C1982" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D1982" s="5">
         <v>2024</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E1982" s="7">
         <v>7.26</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F1982" s="7">
         <v>513.75</v>
       </c>
-      <c r="G92" s="7">
+      <c r="G1982" s="7">
         <v>354.9</v>
       </c>
-      <c r="H92" s="7">
+      <c r="H1982" s="7">
         <v>213.89</v>
       </c>
     </row>
     <row r="1983" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="5" t="s">
+      <c r="A1983" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="B1983" s="5" t="s">
         <v>1660</v>
       </c>
-      <c r="C93" s="13" t="s">
+      <c r="C1983" s="13" t="s">
         <v>1780</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D1983" s="5">
         <v>2025</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E1983" s="7">
         <v>0.64</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F1983" s="7">
         <v>517.04</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G1983" s="7">
         <v>357.18</v>
       </c>
-      <c r="H93" s="7">
+      <c r="H1983" s="7">
         <v>215.26</v>
       </c>
     </row>
     <row r="2340" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="5" t="s">
+      <c r="A2340" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B2340" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C2340" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D2340" s="5">
         <v>2003</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F2340" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="2341" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="5" t="s">
+      <c r="A2341" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="B2341" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C2341" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D2341" s="5">
         <v>2004</v>
       </c>
-      <c r="E95" s="7">
+      <c r="E2341" s="7">
         <v>-1.17</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F2341" s="7">
         <v>98.83</v>
       </c>
     </row>
     <row r="2342" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="5" t="s">
+      <c r="A2342" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B2342" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C2342" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D2342" s="5">
         <v>2005</v>
       </c>
-      <c r="E96" s="7">
+      <c r="E2342" s="7">
         <v>9.0399999999999991</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F2342" s="7">
         <v>107.76</v>
       </c>
     </row>
     <row r="2343" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="5" t="s">
+      <c r="A2343" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B2343" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C2343" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D2343" s="5">
         <v>2006</v>
       </c>
-      <c r="E97" s="7">
+      <c r="E2343" s="7">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F2343" s="7">
         <v>108.35</v>
       </c>
     </row>
     <row r="2344" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="5" t="s">
+      <c r="A2344" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B2344" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C2344" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D2344" s="5">
         <v>2007</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E2344" s="7">
         <v>14.56</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F2344" s="7">
         <v>124.13</v>
       </c>
     </row>
     <row r="2345" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="5" t="s">
+      <c r="A2345" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B2345" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C2345" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D2345" s="5">
         <v>2008</v>
       </c>
-      <c r="E99" s="7">
+      <c r="E2345" s="7">
         <v>-3.64</v>
       </c>
-      <c r="F99" s="7">
+      <c r="F2345" s="7">
         <v>119.61</v>
       </c>
     </row>
     <row r="2346" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="5" t="s">
+      <c r="A2346" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B2346" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C100" s="13" t="s">
+      <c r="C2346" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D2346" s="5">
         <v>2009</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E2346" s="7">
         <v>1.57</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F2346" s="7">
         <v>121.49</v>
       </c>
     </row>
     <row r="2347" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="5" t="s">
+      <c r="A2347" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B2347" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C2347" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D2347" s="5">
         <v>2010</v>
       </c>
-      <c r="E101" s="7">
+      <c r="E2347" s="7">
         <v>2.46</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F2347" s="7">
         <v>124.49</v>
       </c>
     </row>
     <row r="2348" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="5" t="s">
+      <c r="A2348" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B2348" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C2348" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D2348" s="5">
         <v>2011</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E2348" s="7">
         <v>-0.92</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F2348" s="7">
         <v>123.34</v>
       </c>
     </row>
     <row r="2349" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="5" t="s">
+      <c r="A2349" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B2349" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C2349" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D2349" s="5">
         <v>2012</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E2349" s="7">
         <v>7.07</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F2349" s="7">
         <v>132.06</v>
       </c>
     </row>
     <row r="2350" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="5" t="s">
+      <c r="A2350" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B2350" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C2350" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D2350" s="5">
         <v>2013</v>
       </c>
-      <c r="E104" s="7">
+      <c r="E2350" s="7">
         <v>-3.62</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F2350" s="7">
         <v>127.28</v>
       </c>
     </row>
     <row r="2351" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="5" t="s">
+      <c r="A2351" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B2351" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C2351" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D2351" s="5">
         <v>2014</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E2351" s="7">
         <v>13</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F2351" s="7">
         <v>143.83000000000001</v>
       </c>
     </row>
     <row r="2352" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="5" t="s">
+      <c r="A2352" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B2352" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C106" s="13" t="s">
+      <c r="C2352" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D2352" s="5">
         <v>2015</v>
       </c>
-      <c r="E106" s="7">
+      <c r="E2352" s="7">
         <v>-7.16</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F2352" s="7">
         <v>133.53</v>
       </c>
     </row>
     <row r="2353" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="5" t="s">
+      <c r="A2353" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B2353" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C2353" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D2353" s="5">
         <v>2016</v>
       </c>
-      <c r="E107" s="7">
+      <c r="E2353" s="7">
         <v>7.75</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F2353" s="7">
         <v>143.87</v>
       </c>
     </row>
     <row r="2354" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="5" t="s">
+      <c r="A2354" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B2354" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C2354" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D2354" s="5">
         <v>2017</v>
       </c>
-      <c r="E108" s="7">
+      <c r="E2354" s="7">
         <v>2.16</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F2354" s="7">
         <v>146.97999999999999</v>
       </c>
     </row>
     <row r="2355" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="5" t="s">
+      <c r="A2355" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B2355" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C2355" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D2355" s="5">
         <v>2018</v>
       </c>
-      <c r="E109" s="7">
+      <c r="E2355" s="7">
         <v>0.09</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F2355" s="7">
         <v>147.11000000000001</v>
       </c>
     </row>
     <row r="2356" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="5" t="s">
+      <c r="A2356" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B2356" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="C2356" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D2356" s="5">
         <v>2019</v>
       </c>
-      <c r="E110" s="7">
+      <c r="E2356" s="7">
         <v>0.62</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F2356" s="7">
         <v>148.03</v>
       </c>
     </row>
     <row r="2357" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
+      <c r="A2357" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B2357" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C2357" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D2357" s="5">
         <v>2020</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E2357" s="7">
         <v>13.2</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F2357" s="7">
         <v>167.56</v>
       </c>
     </row>
     <row r="2358" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
+      <c r="A2358" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B2358" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C2358" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D2358" s="5">
         <v>2021</v>
       </c>
-      <c r="E112" s="7">
+      <c r="E2358" s="7">
         <v>7.25</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F2358" s="7">
         <v>179.72</v>
       </c>
     </row>
     <row r="2359" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
+      <c r="A2359" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B2359" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C2359" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D2359" s="5">
         <v>2022</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E2359" s="7">
         <v>3.93</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F2359" s="7">
         <v>186.78</v>
       </c>
     </row>
     <row r="2360" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
+      <c r="A2360" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B2360" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C2360" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D2360" s="5">
         <v>2023</v>
       </c>
     </row>
     <row r="2361" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
+      <c r="A2361" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B2361" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C2361" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D2361" s="5">
         <v>2024</v>
       </c>
     </row>
     <row r="2362" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
+      <c r="A2362" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B2362" s="5" t="s">
         <v>1709</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C2362" s="13" t="s">
         <v>1791</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D2362" s="5">
         <v>2025</v>
       </c>
     </row>
     <row r="10740" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
+      <c r="A10740" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B10740" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C10740" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D117" s="5">
+      <c r="D10740" s="5">
         <v>1975</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F10740" s="7">
         <v>100</v>
       </c>
-      <c r="G117" s="7">
+      <c r="G10740" s="7">
         <v>25.83</v>
       </c>
-      <c r="H117" s="7">
+      <c r="H10740" s="7">
         <v>26.38</v>
       </c>
     </row>
     <row r="10741" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
+      <c r="A10741" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B10741" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C118" s="13" t="s">
+      <c r="C10741" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D10741" s="5">
         <v>1976</v>
       </c>
-      <c r="E118" s="7">
+      <c r="E10741" s="7">
         <v>6.58</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F10741" s="7">
         <v>106.58</v>
       </c>
-      <c r="G118" s="7">
+      <c r="G10741" s="7">
         <v>27.53</v>
       </c>
-      <c r="H118" s="7">
+      <c r="H10741" s="7">
         <v>28.11</v>
       </c>
     </row>
     <row r="10742" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="5" t="s">
+      <c r="A10742" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B10742" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C119" s="13" t="s">
+      <c r="C10742" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D10742" s="5">
         <v>1977</v>
       </c>
-      <c r="E119" s="7">
+      <c r="E10742" s="7">
         <v>-0.02</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F10742" s="7">
         <v>106.57</v>
       </c>
-      <c r="G119" s="7">
+      <c r="G10742" s="7">
         <v>27.53</v>
       </c>
-      <c r="H119" s="7">
+      <c r="H10742" s="7">
         <v>28.11</v>
       </c>
     </row>
     <row r="10743" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" s="5" t="s">
+      <c r="A10743" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B10743" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C120" s="13" t="s">
+      <c r="C10743" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D10743" s="5">
         <v>1978</v>
       </c>
-      <c r="E120" s="7">
+      <c r="E10743" s="7">
         <v>23.06</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F10743" s="7">
         <v>131.13999999999999</v>
       </c>
-      <c r="G120" s="7">
+      <c r="G10743" s="7">
         <v>33.869999999999997</v>
       </c>
-      <c r="H120" s="7">
+      <c r="H10743" s="7">
         <v>34.590000000000003</v>
       </c>
     </row>
     <row r="10744" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="5" t="s">
+      <c r="A10744" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B10744" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C121" s="13" t="s">
+      <c r="C10744" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D10744" s="5">
         <v>1979</v>
       </c>
-      <c r="E121" s="7">
+      <c r="E10744" s="7">
         <v>22.56</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F10744" s="7">
         <v>160.72</v>
       </c>
-      <c r="G121" s="7">
+      <c r="G10744" s="7">
         <v>41.51</v>
       </c>
-      <c r="H121" s="7">
+      <c r="H10744" s="7">
         <v>42.39</v>
       </c>
     </row>
     <row r="10745" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
+      <c r="A10745" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B10745" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C122" s="13" t="s">
+      <c r="C10745" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D10745" s="5">
         <v>1980</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E10745" s="7">
         <v>6.95</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F10745" s="7">
         <v>171.89</v>
       </c>
-      <c r="G122" s="7">
+      <c r="G10745" s="7">
         <v>44.4</v>
       </c>
-      <c r="H122" s="7">
+      <c r="H10745" s="7">
         <v>45.34</v>
       </c>
     </row>
     <row r="10746" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="5" t="s">
+      <c r="A10746" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B10746" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C123" s="13" t="s">
+      <c r="C10746" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D123" s="5">
+      <c r="D10746" s="5">
         <v>1981</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E10746" s="7">
         <v>3.87</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F10746" s="7">
         <v>178.55</v>
       </c>
-      <c r="G123" s="7">
+      <c r="G10746" s="7">
         <v>46.12</v>
       </c>
-      <c r="H123" s="7">
+      <c r="H10746" s="7">
         <v>47.1</v>
       </c>
     </row>
     <row r="10747" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="5" t="s">
+      <c r="A10747" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B10747" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C124" s="13" t="s">
+      <c r="C10747" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D10747" s="5">
         <v>1982</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E10747" s="7">
         <v>4.9400000000000004</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F10747" s="7">
         <v>187.37</v>
       </c>
-      <c r="G124" s="7">
+      <c r="G10747" s="7">
         <v>48.4</v>
       </c>
-      <c r="H124" s="7">
+      <c r="H10747" s="7">
         <v>49.42</v>
       </c>
     </row>
     <row r="10748" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="5" t="s">
+      <c r="A10748" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B10748" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C125" s="13" t="s">
+      <c r="C10748" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D125" s="5">
+      <c r="D10748" s="5">
         <v>1983</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E10748" s="7">
         <v>5.35</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F10748" s="7">
         <v>197.39</v>
       </c>
-      <c r="G125" s="7">
+      <c r="G10748" s="7">
         <v>50.98</v>
       </c>
-      <c r="H125" s="7">
+      <c r="H10748" s="7">
         <v>52.06</v>
       </c>
     </row>
     <row r="10749" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="5" t="s">
+      <c r="A10749" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B10749" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C126" s="13" t="s">
+      <c r="C10749" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D10749" s="5">
         <v>1984</v>
       </c>
-      <c r="E126" s="7">
+      <c r="E10749" s="7">
         <v>9.59</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F10749" s="7">
         <v>216.32</v>
       </c>
-      <c r="G126" s="7">
+      <c r="G10749" s="7">
         <v>55.87</v>
       </c>
-      <c r="H126" s="7">
+      <c r="H10749" s="7">
         <v>57.06</v>
       </c>
     </row>
     <row r="10750" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="5" t="s">
+      <c r="A10750" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B10750" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C127" s="13" t="s">
+      <c r="C10750" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D10750" s="5">
         <v>1985</v>
       </c>
-      <c r="E127" s="7">
+      <c r="E10750" s="7">
         <v>12.08</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F10750" s="7">
         <v>242.45</v>
       </c>
-      <c r="G127" s="7">
+      <c r="G10750" s="7">
         <v>62.62</v>
       </c>
-      <c r="H127" s="7">
+      <c r="H10750" s="7">
         <v>63.95</v>
       </c>
     </row>
     <row r="10751" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="5" t="s">
+      <c r="A10751" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B10751" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C128" s="13" t="s">
+      <c r="C10751" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D10751" s="5">
         <v>1986</v>
       </c>
-      <c r="E128" s="7">
+      <c r="E10751" s="7">
         <v>15.52</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F10751" s="7">
         <v>280.08</v>
       </c>
-      <c r="G128" s="7">
+      <c r="G10751" s="7">
         <v>72.34</v>
       </c>
-      <c r="H128" s="7">
+      <c r="H10751" s="7">
         <v>73.88</v>
       </c>
     </row>
     <row r="10752" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="5" t="s">
+      <c r="A10752" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B10752" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C10752" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D10752" s="5">
         <v>1987</v>
       </c>
-      <c r="E129" s="7">
+      <c r="E10752" s="7">
         <v>22.98</v>
       </c>
-      <c r="F129" s="7">
+      <c r="F10752" s="7">
         <v>344.43</v>
       </c>
-      <c r="G129" s="7">
+      <c r="G10752" s="7">
         <v>88.97</v>
       </c>
-      <c r="H129" s="7">
+      <c r="H10752" s="7">
         <v>90.85</v>
       </c>
     </row>
     <row r="10753" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="5" t="s">
+      <c r="A10753" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B10753" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C130" s="13" t="s">
+      <c r="C10753" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D130" s="5">
+      <c r="D10753" s="5">
         <v>1988</v>
       </c>
-      <c r="E130" s="7">
+      <c r="E10753" s="7">
         <v>18.8</v>
       </c>
-      <c r="F130" s="7">
+      <c r="F10753" s="7">
         <v>409.19</v>
       </c>
-      <c r="G130" s="7">
+      <c r="G10753" s="7">
         <v>105.69</v>
       </c>
-      <c r="H130" s="7">
+      <c r="H10753" s="7">
         <v>107.93</v>
       </c>
     </row>
     <row r="10754" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="5" t="s">
+      <c r="A10754" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B10754" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C131" s="13" t="s">
+      <c r="C10754" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D131" s="5">
+      <c r="D10754" s="5">
         <v>1989</v>
       </c>
-      <c r="E131" s="7">
+      <c r="E10754" s="7">
         <v>-0.91</v>
       </c>
-      <c r="F131" s="7">
+      <c r="F10754" s="7">
         <v>405.48</v>
       </c>
-      <c r="G131" s="7">
+      <c r="G10754" s="7">
         <v>104.73</v>
       </c>
-      <c r="H131" s="7">
+      <c r="H10754" s="7">
         <v>106.95</v>
       </c>
     </row>
     <row r="10755" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="5" t="s">
+      <c r="A10755" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B10755" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C132" s="13" t="s">
+      <c r="C10755" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D10755" s="5">
         <v>1990</v>
       </c>
-      <c r="E132" s="7">
+      <c r="E10755" s="7">
         <v>-4.5199999999999996</v>
       </c>
-      <c r="F132" s="7">
+      <c r="F10755" s="7">
         <v>387.15</v>
       </c>
-      <c r="G132" s="7">
+      <c r="G10755" s="7">
         <v>100</v>
       </c>
-      <c r="H132" s="7">
+      <c r="H10755" s="7">
         <v>102.12</v>
       </c>
     </row>
     <row r="10756" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="5" t="s">
+      <c r="A10756" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B10756" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C133" s="13" t="s">
+      <c r="C10756" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D133" s="5">
+      <c r="D10756" s="5">
         <v>1991</v>
       </c>
-      <c r="E133" s="7">
+      <c r="E10756" s="7">
         <v>-5.71</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F10756" s="7">
         <v>365.04</v>
       </c>
-      <c r="G133" s="7">
+      <c r="G10756" s="7">
         <v>94.29</v>
       </c>
-      <c r="H133" s="7">
+      <c r="H10756" s="7">
         <v>96.28</v>
       </c>
     </row>
     <row r="10757" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="5" t="s">
+      <c r="A10757" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B10757" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C134" s="13" t="s">
+      <c r="C10757" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D10757" s="5">
         <v>1992</v>
       </c>
-      <c r="E134" s="7">
+      <c r="E10757" s="7">
         <v>-2.86</v>
       </c>
-      <c r="F134" s="7">
+      <c r="F10757" s="7">
         <v>354.61</v>
       </c>
-      <c r="G134" s="7">
+      <c r="G10757" s="7">
         <v>91.59</v>
       </c>
-      <c r="H134" s="7">
+      <c r="H10757" s="7">
         <v>93.53</v>
       </c>
     </row>
     <row r="10758" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="5" t="s">
+      <c r="A10758" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B10758" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C135" s="13" t="s">
+      <c r="C10758" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D10758" s="5">
         <v>1993</v>
       </c>
-      <c r="E135" s="7">
+      <c r="E10758" s="7">
         <v>-3.83</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F10758" s="7">
         <v>341.02</v>
       </c>
-      <c r="G135" s="7">
+      <c r="G10758" s="7">
         <v>88.08</v>
       </c>
-      <c r="H135" s="7">
+      <c r="H10758" s="7">
         <v>89.95</v>
       </c>
     </row>
     <row r="10759" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="5" t="s">
+      <c r="A10759" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B10759" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C136" s="13" t="s">
+      <c r="C10759" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D10759" s="5">
         <v>1994</v>
       </c>
-      <c r="E136" s="7">
+      <c r="E10759" s="7">
         <v>-2.82</v>
       </c>
-      <c r="F136" s="7">
+      <c r="F10759" s="7">
         <v>331.39</v>
       </c>
-      <c r="G136" s="7">
+      <c r="G10759" s="7">
         <v>85.6</v>
       </c>
-      <c r="H136" s="7">
+      <c r="H10759" s="7">
         <v>87.41</v>
       </c>
     </row>
     <row r="10760" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A137" s="5" t="s">
+      <c r="A10760" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B10760" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C137" s="13" t="s">
+      <c r="C10760" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D10760" s="5">
         <v>1995</v>
       </c>
-      <c r="E137" s="7">
+      <c r="E10760" s="7">
         <v>-2.3199999999999998</v>
       </c>
-      <c r="F137" s="7">
+      <c r="F10760" s="7">
         <v>323.7</v>
       </c>
-      <c r="G137" s="7">
+      <c r="G10760" s="7">
         <v>83.61</v>
       </c>
-      <c r="H137" s="7">
+      <c r="H10760" s="7">
         <v>85.38</v>
       </c>
     </row>
     <row r="10761" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A138" s="5" t="s">
+      <c r="A10761" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B10761" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C138" s="13" t="s">
+      <c r="C10761" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D10761" s="5">
         <v>1996</v>
       </c>
-      <c r="E138" s="7">
+      <c r="E10761" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F138" s="7">
+      <c r="F10761" s="7">
         <v>323.93</v>
       </c>
-      <c r="G138" s="7">
+      <c r="G10761" s="7">
         <v>83.67</v>
       </c>
-      <c r="H138" s="7">
+      <c r="H10761" s="7">
         <v>85.44</v>
       </c>
     </row>
     <row r="10762" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A139" s="5" t="s">
+      <c r="A10762" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="B10762" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C139" s="13" t="s">
+      <c r="C10762" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D10762" s="5">
         <v>1997</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E10762" s="7">
         <v>-0.09</v>
       </c>
-      <c r="F139" s="7">
+      <c r="F10762" s="7">
         <v>323.64</v>
       </c>
-      <c r="G139" s="7">
+      <c r="G10762" s="7">
         <v>83.6</v>
       </c>
-      <c r="H139" s="7">
+      <c r="H10762" s="7">
         <v>85.36</v>
       </c>
     </row>
     <row r="10763" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A140" s="5" t="s">
+      <c r="A10763" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B10763" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C140" s="13" t="s">
+      <c r="C10763" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D10763" s="5">
         <v>1998</v>
       </c>
-      <c r="E140" s="7">
+      <c r="E10763" s="7">
         <v>4.09</v>
       </c>
-      <c r="F140" s="7">
+      <c r="F10763" s="7">
         <v>336.89</v>
       </c>
-      <c r="G140" s="7">
+      <c r="G10763" s="7">
         <v>87.02</v>
       </c>
-      <c r="H140" s="7">
+      <c r="H10763" s="7">
         <v>88.86</v>
       </c>
     </row>
     <row r="10764" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A141" s="5" t="s">
+      <c r="A10764" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B10764" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C141" s="13" t="s">
+      <c r="C10764" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D10764" s="5">
         <v>1999</v>
       </c>
-      <c r="E141" s="7">
+      <c r="E10764" s="7">
         <v>4.12</v>
       </c>
-      <c r="F141" s="7">
+      <c r="F10764" s="7">
         <v>350.78</v>
       </c>
-      <c r="G141" s="7">
+      <c r="G10764" s="7">
         <v>90.6</v>
       </c>
-      <c r="H141" s="7">
+      <c r="H10764" s="7">
         <v>92.52</v>
       </c>
     </row>
     <row r="10765" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A142" s="5" t="s">
+      <c r="A10765" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B10765" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C142" s="13" t="s">
+      <c r="C10765" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D10765" s="5">
         <v>2000</v>
       </c>
-      <c r="E142" s="7">
+      <c r="E10765" s="7">
         <v>8.08</v>
       </c>
-      <c r="F142" s="7">
+      <c r="F10765" s="7">
         <v>379.13</v>
       </c>
-      <c r="G142" s="7">
+      <c r="G10765" s="7">
         <v>97.93</v>
       </c>
-      <c r="H142" s="7">
+      <c r="H10765" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="10766" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A143" s="5" t="s">
+      <c r="A10766" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="B10766" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C143" s="13" t="s">
+      <c r="C10766" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D10766" s="5">
         <v>2001</v>
       </c>
-      <c r="E143" s="7">
+      <c r="E10766" s="7">
         <v>6.71</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F10766" s="7">
         <v>404.57</v>
       </c>
-      <c r="G143" s="7">
+      <c r="G10766" s="7">
         <v>104.5</v>
       </c>
-      <c r="H143" s="7">
+      <c r="H10766" s="7">
         <v>106.71</v>
       </c>
     </row>
     <row r="10767" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A144" s="5" t="s">
+      <c r="A10767" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B10767" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C144" s="13" t="s">
+      <c r="C10767" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D10767" s="5">
         <v>2002</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E10767" s="7">
         <v>7.53</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F10767" s="7">
         <v>435.05</v>
       </c>
-      <c r="G144" s="7">
+      <c r="G10767" s="7">
         <v>112.37</v>
       </c>
-      <c r="H144" s="7">
+      <c r="H10767" s="7">
         <v>114.75</v>
       </c>
     </row>
     <row r="10768" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A145" s="5" t="s">
+      <c r="A10768" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B10768" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C145" s="13" t="s">
+      <c r="C10768" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D10768" s="5">
         <v>2003</v>
       </c>
-      <c r="E145" s="7">
+      <c r="E10768" s="7">
         <v>5.27</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F10768" s="7">
         <v>457.98</v>
       </c>
-      <c r="G145" s="7">
+      <c r="G10768" s="7">
         <v>118.29</v>
       </c>
-      <c r="H145" s="7">
+      <c r="H10768" s="7">
         <v>120.8</v>
       </c>
     </row>
     <row r="10769" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A146" s="5" t="s">
+      <c r="A10769" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="B10769" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C146" s="13" t="s">
+      <c r="C10769" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D10769" s="5">
         <v>2004</v>
       </c>
-      <c r="E146" s="7">
+      <c r="E10769" s="7">
         <v>10.039999999999999</v>
       </c>
-      <c r="F146" s="7">
+      <c r="F10769" s="7">
         <v>503.96</v>
       </c>
-      <c r="G146" s="7">
+      <c r="G10769" s="7">
         <v>130.16999999999999</v>
       </c>
-      <c r="H146" s="7">
+      <c r="H10769" s="7">
         <v>132.93</v>
       </c>
     </row>
     <row r="10770" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A147" s="5" t="s">
+      <c r="A10770" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B10770" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C147" s="13" t="s">
+      <c r="C10770" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D147" s="5">
+      <c r="D10770" s="5">
         <v>2005</v>
       </c>
-      <c r="E147" s="7">
+      <c r="E10770" s="7">
         <v>10.89</v>
       </c>
-      <c r="F147" s="7">
+      <c r="F10770" s="7">
         <v>558.82000000000005</v>
       </c>
-      <c r="G147" s="7">
+      <c r="G10770" s="7">
         <v>144.34</v>
       </c>
-      <c r="H147" s="7">
+      <c r="H10770" s="7">
         <v>147.38999999999999</v>
       </c>
     </row>
     <row r="10771" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A148" s="5" t="s">
+      <c r="A10771" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B10771" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C148" s="13" t="s">
+      <c r="C10771" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D148" s="5">
+      <c r="D10771" s="5">
         <v>2006</v>
       </c>
-      <c r="E148" s="7">
+      <c r="E10771" s="7">
         <v>5.35</v>
       </c>
-      <c r="F148" s="7">
+      <c r="F10771" s="7">
         <v>588.69000000000005</v>
       </c>
-      <c r="G148" s="7">
+      <c r="G10771" s="7">
         <v>152.06</v>
       </c>
-      <c r="H148" s="7">
+      <c r="H10771" s="7">
         <v>155.27000000000001</v>
       </c>
     </row>
     <row r="10772" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A149" s="5" t="s">
+      <c r="A10772" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B10772" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C149" s="13" t="s">
+      <c r="C10772" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D10772" s="5">
         <v>2007</v>
       </c>
-      <c r="E149" s="7">
+      <c r="E10772" s="7">
         <v>1.1499999999999999</v>
       </c>
-      <c r="F149" s="7">
+      <c r="F10772" s="7">
         <v>595.47</v>
       </c>
-      <c r="G149" s="7">
+      <c r="G10772" s="7">
         <v>153.81</v>
       </c>
-      <c r="H149" s="7">
+      <c r="H10772" s="7">
         <v>157.06</v>
       </c>
     </row>
     <row r="10773" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A150" s="5" t="s">
+      <c r="A10773" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B10773" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C150" s="13" t="s">
+      <c r="C10773" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D10773" s="5">
         <v>2008</v>
       </c>
-      <c r="E150" s="7">
+      <c r="E10773" s="7">
         <v>-2.57</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F10773" s="7">
         <v>580.16</v>
       </c>
-      <c r="G150" s="7">
+      <c r="G10773" s="7">
         <v>149.85</v>
       </c>
-      <c r="H150" s="7">
+      <c r="H10773" s="7">
         <v>153.02000000000001</v>
       </c>
     </row>
     <row r="10774" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A151" s="5" t="s">
+      <c r="A10774" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B10774" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C151" s="13" t="s">
+      <c r="C10774" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D10774" s="5">
         <v>2009</v>
       </c>
-      <c r="E151" s="7">
+      <c r="E10774" s="7">
         <v>-5.31</v>
       </c>
-      <c r="F151" s="7">
+      <c r="F10774" s="7">
         <v>549.37</v>
       </c>
-      <c r="G151" s="7">
+      <c r="G10774" s="7">
         <v>141.9</v>
       </c>
-      <c r="H151" s="7">
+      <c r="H10774" s="7">
         <v>144.9</v>
       </c>
     </row>
     <row r="10775" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A152" s="5" t="s">
+      <c r="A10775" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B10775" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C152" s="13" t="s">
+      <c r="C10775" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D10775" s="5">
         <v>2010</v>
       </c>
-      <c r="E152" s="7">
+      <c r="E10775" s="7">
         <v>-2.57</v>
       </c>
-      <c r="F152" s="7">
+      <c r="F10775" s="7">
         <v>535.27</v>
       </c>
-      <c r="G152" s="7">
+      <c r="G10775" s="7">
         <v>138.26</v>
       </c>
-      <c r="H152" s="7">
+      <c r="H10775" s="7">
         <v>141.18</v>
       </c>
     </row>
     <row r="10776" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A153" s="5" t="s">
+      <c r="A10776" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B10776" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C153" s="13" t="s">
+      <c r="C10776" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D10776" s="5">
         <v>2011</v>
       </c>
-      <c r="E153" s="7">
+      <c r="E10776" s="7">
         <v>-2.99</v>
       </c>
-      <c r="F153" s="7">
+      <c r="F10776" s="7">
         <v>519.26</v>
       </c>
-      <c r="G153" s="7">
+      <c r="G10776" s="7">
         <v>134.12</v>
       </c>
-      <c r="H153" s="7">
+      <c r="H10776" s="7">
         <v>136.96</v>
       </c>
     </row>
     <row r="10777" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A154" s="5" t="s">
+      <c r="A10777" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B10777" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C154" s="13" t="s">
+      <c r="C10777" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D10777" s="5">
         <v>2012</v>
       </c>
-      <c r="E154" s="7">
+      <c r="E10777" s="7">
         <v>-2.68</v>
       </c>
-      <c r="F154" s="7">
+      <c r="F10777" s="7">
         <v>505.37</v>
       </c>
-      <c r="G154" s="7">
+      <c r="G10777" s="7">
         <v>130.53</v>
       </c>
-      <c r="H154" s="7">
+      <c r="H10777" s="7">
         <v>133.30000000000001</v>
       </c>
     </row>
     <row r="10778" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A155" s="5" t="s">
+      <c r="A10778" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B10778" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C155" s="13" t="s">
+      <c r="C10778" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D155" s="5">
+      <c r="D10778" s="5">
         <v>2013</v>
       </c>
-      <c r="E155" s="7">
+      <c r="E10778" s="7">
         <v>-0.65</v>
       </c>
-      <c r="F155" s="7">
+      <c r="F10778" s="7">
         <v>502.08</v>
       </c>
-      <c r="G155" s="7">
+      <c r="G10778" s="7">
         <v>129.68</v>
       </c>
-      <c r="H155" s="7">
+      <c r="H10778" s="7">
         <v>132.43</v>
       </c>
     </row>
     <row r="10779" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A156" s="5" t="s">
+      <c r="A10779" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B10779" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C156" s="13" t="s">
+      <c r="C10779" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D156" s="5">
+      <c r="D10779" s="5">
         <v>2014</v>
       </c>
-      <c r="E156" s="7">
+      <c r="E10779" s="7">
         <v>-0.03</v>
       </c>
-      <c r="F156" s="7">
+      <c r="F10779" s="7">
         <v>501.94</v>
       </c>
-      <c r="G156" s="7">
+      <c r="G10779" s="7">
         <v>129.65</v>
       </c>
-      <c r="H156" s="7">
+      <c r="H10779" s="7">
         <v>132.38999999999999</v>
       </c>
     </row>
     <row r="10780" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A157" s="5" t="s">
+      <c r="A10780" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B10780" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C157" s="13" t="s">
+      <c r="C10780" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D157" s="5">
+      <c r="D10780" s="5">
         <v>2015</v>
       </c>
-      <c r="E157" s="7">
+      <c r="E10780" s="7">
         <v>0.77</v>
       </c>
-      <c r="F157" s="7">
+      <c r="F10780" s="7">
         <v>505.81</v>
       </c>
-      <c r="G157" s="7">
+      <c r="G10780" s="7">
         <v>130.65</v>
       </c>
-      <c r="H157" s="7">
+      <c r="H10780" s="7">
         <v>133.41</v>
       </c>
     </row>
     <row r="10781" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" s="5" t="s">
+      <c r="A10781" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B10781" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C158" s="13" t="s">
+      <c r="C10781" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D158" s="5">
+      <c r="D10781" s="5">
         <v>2016</v>
       </c>
-      <c r="E158" s="7">
+      <c r="E10781" s="7">
         <v>0.01</v>
       </c>
-      <c r="F158" s="7">
+      <c r="F10781" s="7">
         <v>505.87</v>
       </c>
-      <c r="G158" s="7">
+      <c r="G10781" s="7">
         <v>130.66</v>
       </c>
-      <c r="H158" s="7">
+      <c r="H10781" s="7">
         <v>133.43</v>
       </c>
     </row>
     <row r="10782" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159" s="5" t="s">
+      <c r="A10782" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B10782" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C159" s="13" t="s">
+      <c r="C10782" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D159" s="5">
+      <c r="D10782" s="5">
         <v>2017</v>
       </c>
-      <c r="E159" s="7">
+      <c r="E10782" s="7">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F159" s="7">
+      <c r="F10782" s="7">
         <v>511.61</v>
       </c>
-      <c r="G159" s="7">
+      <c r="G10782" s="7">
         <v>132.15</v>
       </c>
-      <c r="H159" s="7">
+      <c r="H10782" s="7">
         <v>134.94</v>
       </c>
     </row>
     <row r="10783" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A160" s="5" t="s">
+      <c r="A10783" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B10783" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C160" s="13" t="s">
+      <c r="C10783" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D160" s="5">
+      <c r="D10783" s="5">
         <v>2018</v>
       </c>
-      <c r="E160" s="7">
+      <c r="E10783" s="7">
         <v>0.95</v>
       </c>
-      <c r="F160" s="7">
+      <c r="F10783" s="7">
         <v>516.48</v>
       </c>
-      <c r="G160" s="7">
+      <c r="G10783" s="7">
         <v>133.4</v>
       </c>
-      <c r="H160" s="7">
+      <c r="H10783" s="7">
         <v>136.22999999999999</v>
       </c>
     </row>
     <row r="10784" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A161" s="5" t="s">
+      <c r="A10784" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B10784" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C161" s="13" t="s">
+      <c r="C10784" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D161" s="5">
+      <c r="D10784" s="5">
         <v>2019</v>
       </c>
-      <c r="E161" s="7">
+      <c r="E10784" s="7">
         <v>2.17</v>
       </c>
-      <c r="F161" s="7">
+      <c r="F10784" s="7">
         <v>527.71</v>
       </c>
-      <c r="G161" s="7">
+      <c r="G10784" s="7">
         <v>136.30000000000001</v>
       </c>
-      <c r="H161" s="7">
+      <c r="H10784" s="7">
         <v>139.19</v>
       </c>
     </row>
     <row r="10785" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A162" s="5" t="s">
+      <c r="A10785" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B10785" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C162" s="13" t="s">
+      <c r="C10785" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D162" s="5">
+      <c r="D10785" s="5">
         <v>2020</v>
       </c>
-      <c r="E162" s="7">
+      <c r="E10785" s="7">
         <v>2.77</v>
       </c>
-      <c r="F162" s="7">
+      <c r="F10785" s="7">
         <v>542.30999999999995</v>
       </c>
-      <c r="G162" s="7">
+      <c r="G10785" s="7">
         <v>140.08000000000001</v>
       </c>
-      <c r="H162" s="7">
+      <c r="H10785" s="7">
         <v>143.04</v>
       </c>
     </row>
     <row r="10786" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A163" s="5" t="s">
+      <c r="A10786" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B10786" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C163" s="13" t="s">
+      <c r="C10786" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D163" s="5">
+      <c r="D10786" s="5">
         <v>2021</v>
       </c>
-      <c r="E163" s="7">
+      <c r="E10786" s="7">
         <v>10.72</v>
       </c>
-      <c r="F163" s="7">
+      <c r="F10786" s="7">
         <v>600.44000000000005</v>
       </c>
-      <c r="G163" s="7">
+      <c r="G10786" s="7">
         <v>155.09</v>
       </c>
-      <c r="H163" s="7">
+      <c r="H10786" s="7">
         <v>158.37</v>
       </c>
     </row>
     <row r="10787" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A164" s="5" t="s">
+      <c r="A10787" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B10787" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C164" s="13" t="s">
+      <c r="C10787" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D164" s="5">
+      <c r="D10787" s="5">
         <v>2022</v>
       </c>
-      <c r="E164" s="7">
+      <c r="E10787" s="7">
         <v>13.49</v>
       </c>
-      <c r="F164" s="7">
+      <c r="F10787" s="7">
         <v>681.41</v>
       </c>
-      <c r="G164" s="7">
+      <c r="G10787" s="7">
         <v>176</v>
       </c>
-      <c r="H164" s="7">
+      <c r="H10787" s="7">
         <v>179.73</v>
       </c>
     </row>
     <row r="10788" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A165" s="5" t="s">
+      <c r="A10788" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B10788" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C165" s="13" t="s">
+      <c r="C10788" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D165" s="5">
+      <c r="D10788" s="5">
         <v>2023</v>
       </c>
-      <c r="E165" s="7">
+      <c r="E10788" s="7">
         <v>10.83</v>
       </c>
-      <c r="F165" s="7">
+      <c r="F10788" s="7">
         <v>755.19</v>
       </c>
-      <c r="G165" s="7">
+      <c r="G10788" s="7">
         <v>195.06</v>
       </c>
-      <c r="H165" s="7">
+      <c r="H10788" s="7">
         <v>199.19</v>
       </c>
     </row>
     <row r="10789" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A166" s="5" t="s">
+      <c r="A10789" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B10789" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C166" s="13" t="s">
+      <c r="C10789" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D166" s="5">
+      <c r="D10789" s="5">
         <v>2024</v>
       </c>
-      <c r="E166" s="7">
+      <c r="E10789" s="7">
         <v>9.74</v>
       </c>
-      <c r="F166" s="7">
+      <c r="F10789" s="7">
         <v>828.74</v>
       </c>
-      <c r="G166" s="7">
+      <c r="G10789" s="7">
         <v>214.06</v>
       </c>
-      <c r="H166" s="7">
+      <c r="H10789" s="7">
         <v>218.59</v>
       </c>
     </row>
     <row r="10790" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A167" s="5" t="s">
+      <c r="A10790" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B10790" s="5" t="s">
         <v>1717</v>
       </c>
-      <c r="C167" s="13" t="s">
+      <c r="C10790" s="13" t="s">
         <v>2000</v>
       </c>
-      <c r="D167" s="5">
+      <c r="D10790" s="5">
         <v>2025</v>
       </c>
-      <c r="E167" s="7">
+      <c r="E10790" s="7">
         <v>5.74</v>
       </c>
-      <c r="F167" s="7">
+      <c r="F10790" s="7">
         <v>876.34</v>
       </c>
-      <c r="G167" s="7">
+      <c r="G10790" s="7">
         <v>226.35</v>
       </c>
-      <c r="H167" s="7">
+      <c r="H10790" s="7">
         <v>231.14</v>
       </c>
     </row>
     <row r="11179" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A168" s="5" t="s">
+      <c r="A11179" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B11179" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C168" s="14">
+      <c r="C11179" s="14">
         <v>10001</v>
       </c>
-      <c r="D168" s="5">
+      <c r="D11179" s="5">
         <v>1979</v>
       </c>
-      <c r="F168" s="7">
+      <c r="F11179" s="7">
         <v>100</v>
       </c>
-      <c r="G168" s="7">
+      <c r="G11179" s="7">
         <v>49.25</v>
       </c>
-      <c r="H168" s="7">
+      <c r="H11179" s="7">
         <v>42.13</v>
       </c>
     </row>
     <row r="11180" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A169" s="5" t="s">
+      <c r="A11180" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B11180" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C169" s="14">
+      <c r="C11180" s="14">
         <v>10001</v>
       </c>
-      <c r="D169" s="5">
+      <c r="D11180" s="5">
         <v>1980</v>
       </c>
-      <c r="E169" s="7">
+      <c r="E11180" s="7">
         <v>27.33</v>
       </c>
-      <c r="F169" s="7">
+      <c r="F11180" s="7">
         <v>127.33</v>
       </c>
-      <c r="G169" s="7">
+      <c r="G11180" s="7">
         <v>62.72</v>
       </c>
-      <c r="H169" s="7">
+      <c r="H11180" s="7">
         <v>53.65</v>
       </c>
     </row>
     <row r="11181" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A170" s="5" t="s">
+      <c r="A11181" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B11181" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C170" s="14">
+      <c r="C11181" s="14">
         <v>10001</v>
       </c>
-      <c r="D170" s="5">
+      <c r="D11181" s="5">
         <v>1981</v>
       </c>
     </row>
     <row r="11182" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A171" s="5" t="s">
+      <c r="A11182" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B11182" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C171" s="14">
+      <c r="C11182" s="14">
         <v>10001</v>
       </c>
-      <c r="D171" s="5">
+      <c r="D11182" s="5">
         <v>1982</v>
       </c>
-      <c r="F171" s="7">
+      <c r="F11182" s="7">
         <v>133.74</v>
       </c>
-      <c r="G171" s="7">
+      <c r="G11182" s="7">
         <v>65.87</v>
       </c>
-      <c r="H171" s="7">
+      <c r="H11182" s="7">
         <v>56.35</v>
       </c>
     </row>
     <row r="11183" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A172" s="5" t="s">
+      <c r="A11183" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B172" s="5" t="s">
+      <c r="B11183" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C172" s="14">
+      <c r="C11183" s="14">
         <v>10001</v>
       </c>
-      <c r="D172" s="5">
+      <c r="D11183" s="5">
         <v>1983</v>
       </c>
-      <c r="E172" s="7">
+      <c r="E11183" s="7">
         <v>-4.01</v>
       </c>
-      <c r="F172" s="7">
+      <c r="F11183" s="7">
         <v>128.37</v>
       </c>
-      <c r="G172" s="7">
+      <c r="G11183" s="7">
         <v>63.23</v>
       </c>
-      <c r="H172" s="7">
+      <c r="H11183" s="7">
         <v>54.09</v>
       </c>
     </row>
     <row r="11184" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A173" s="5" t="s">
+      <c r="A11184" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B11184" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C173" s="14">
+      <c r="C11184" s="14">
         <v>10001</v>
       </c>
-      <c r="D173" s="5">
+      <c r="D11184" s="5">
         <v>1984</v>
       </c>
-      <c r="E173" s="7">
+      <c r="E11184" s="7">
         <v>6.93</v>
       </c>
-      <c r="F173" s="7">
+      <c r="F11184" s="7">
         <v>137.27000000000001</v>
       </c>
-      <c r="G173" s="7">
+      <c r="G11184" s="7">
         <v>67.61</v>
       </c>
-      <c r="H173" s="7">
+      <c r="H11184" s="7">
         <v>57.84</v>
       </c>
     </row>
     <row r="11185" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A174" s="5" t="s">
+      <c r="A11185" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B11185" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C174" s="14">
+      <c r="C11185" s="14">
         <v>10001</v>
       </c>
-      <c r="D174" s="5">
+      <c r="D11185" s="5">
         <v>1985</v>
       </c>
-      <c r="E174" s="7">
+      <c r="E11185" s="7">
         <v>5.04</v>
       </c>
-      <c r="F174" s="7">
+      <c r="F11185" s="7">
         <v>144.19</v>
       </c>
-      <c r="G174" s="7">
+      <c r="G11185" s="7">
         <v>71.02</v>
       </c>
-      <c r="H174" s="7">
+      <c r="H11185" s="7">
         <v>60.75</v>
       </c>
     </row>
     <row r="11186" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A175" s="5" t="s">
+      <c r="A11186" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B11186" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C175" s="14">
+      <c r="C11186" s="14">
         <v>10001</v>
       </c>
-      <c r="D175" s="5">
+      <c r="D11186" s="5">
         <v>1986</v>
       </c>
-      <c r="E175" s="7">
+      <c r="E11186" s="7">
         <v>6.89</v>
       </c>
-      <c r="F175" s="7">
+      <c r="F11186" s="7">
         <v>154.13</v>
       </c>
-      <c r="G175" s="7">
+      <c r="G11186" s="7">
         <v>75.92</v>
       </c>
-      <c r="H175" s="7">
+      <c r="H11186" s="7">
         <v>64.94</v>
       </c>
     </row>
     <row r="11187" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A176" s="5" t="s">
+      <c r="A11187" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B11187" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C176" s="14">
+      <c r="C11187" s="14">
         <v>10001</v>
       </c>
-      <c r="D176" s="5">
+      <c r="D11187" s="5">
         <v>1987</v>
       </c>
-      <c r="E176" s="7">
+      <c r="E11187" s="7">
         <v>7.59</v>
       </c>
-      <c r="F176" s="7">
+      <c r="F11187" s="7">
         <v>165.82</v>
       </c>
-      <c r="G176" s="7">
+      <c r="G11187" s="7">
         <v>81.680000000000007</v>
       </c>
-      <c r="H176" s="7">
+      <c r="H11187" s="7">
         <v>69.87</v>
       </c>
     </row>
     <row r="11188" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A177" s="5" t="s">
+      <c r="A11188" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B11188" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C177" s="14">
+      <c r="C11188" s="14">
         <v>10001</v>
       </c>
-      <c r="D177" s="5">
+      <c r="D11188" s="5">
         <v>1988</v>
       </c>
-      <c r="E177" s="7">
+      <c r="E11188" s="7">
         <v>8.61</v>
       </c>
-      <c r="F177" s="7">
+      <c r="F11188" s="7">
         <v>180.11</v>
       </c>
-      <c r="G177" s="7">
+      <c r="G11188" s="7">
         <v>88.71</v>
       </c>
-      <c r="H177" s="7">
+      <c r="H11188" s="7">
         <v>75.89</v>
       </c>
     </row>
     <row r="11189" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A178" s="5" t="s">
+      <c r="A11189" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B11189" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C178" s="14">
+      <c r="C11189" s="14">
         <v>10001</v>
       </c>
-      <c r="D178" s="5">
+      <c r="D11189" s="5">
         <v>1989</v>
       </c>
-      <c r="E178" s="7">
+      <c r="E11189" s="7">
         <v>6.48</v>
       </c>
-      <c r="F178" s="7">
+      <c r="F11189" s="7">
         <v>191.78</v>
       </c>
-      <c r="G178" s="7">
+      <c r="G11189" s="7">
         <v>94.46</v>
       </c>
-      <c r="H178" s="7">
+      <c r="H11189" s="7">
         <v>80.81</v>
       </c>
     </row>
     <row r="11190" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A179" s="5" t="s">
+      <c r="A11190" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B11190" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C179" s="14">
+      <c r="C11190" s="14">
         <v>10001</v>
       </c>
-      <c r="D179" s="5">
+      <c r="D11190" s="5">
         <v>1990</v>
       </c>
-      <c r="E179" s="7">
+      <c r="E11190" s="7">
         <v>5.86</v>
       </c>
-      <c r="F179" s="7">
+      <c r="F11190" s="7">
         <v>203.03</v>
       </c>
-      <c r="G179" s="7">
+      <c r="G11190" s="7">
         <v>100</v>
       </c>
-      <c r="H179" s="7">
+      <c r="H11190" s="7">
         <v>85.54</v>
       </c>
     </row>
     <row r="11191" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A180" s="5" t="s">
+      <c r="A11191" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B11191" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C180" s="14">
+      <c r="C11191" s="14">
         <v>10001</v>
       </c>
-      <c r="D180" s="5">
+      <c r="D11191" s="5">
         <v>1991</v>
       </c>
-      <c r="E180" s="7">
+      <c r="E11191" s="7">
         <v>3.87</v>
       </c>
-      <c r="F180" s="7">
+      <c r="F11191" s="7">
         <v>210.89</v>
       </c>
-      <c r="G180" s="7">
+      <c r="G11191" s="7">
         <v>103.87</v>
       </c>
-      <c r="H180" s="7">
+      <c r="H11191" s="7">
         <v>88.85</v>
       </c>
     </row>
     <row r="11192" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A181" s="5" t="s">
+      <c r="A11192" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B11192" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C181" s="14">
+      <c r="C11192" s="14">
         <v>10001</v>
       </c>
-      <c r="D181" s="5">
+      <c r="D11192" s="5">
         <v>1992</v>
       </c>
-      <c r="E181" s="7">
+      <c r="E11192" s="7">
         <v>0.52</v>
       </c>
-      <c r="F181" s="7">
+      <c r="F11192" s="7">
         <v>211.98</v>
       </c>
-      <c r="G181" s="7">
+      <c r="G11192" s="7">
         <v>104.41</v>
       </c>
-      <c r="H181" s="7">
+      <c r="H11192" s="7">
         <v>89.31</v>
       </c>
     </row>
     <row r="11193" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A182" s="5" t="s">
+      <c r="A11193" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B11193" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C182" s="14">
+      <c r="C11193" s="14">
         <v>10001</v>
       </c>
-      <c r="D182" s="5">
+      <c r="D11193" s="5">
         <v>1993</v>
       </c>
-      <c r="E182" s="7">
+      <c r="E11193" s="7">
         <v>2.44</v>
       </c>
-      <c r="F182" s="7">
+      <c r="F11193" s="7">
         <v>217.15</v>
       </c>
-      <c r="G182" s="7">
+      <c r="G11193" s="7">
         <v>106.96</v>
       </c>
-      <c r="H182" s="7">
+      <c r="H11193" s="7">
         <v>91.49</v>
       </c>
     </row>
     <row r="11194" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A183" s="5" t="s">
+      <c r="A11194" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B11194" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C183" s="14">
+      <c r="C11194" s="14">
         <v>10001</v>
       </c>
-      <c r="D183" s="5">
+      <c r="D11194" s="5">
         <v>1994</v>
       </c>
-      <c r="E183" s="7">
+      <c r="E11194" s="7">
         <v>-1.32</v>
       </c>
-      <c r="F183" s="7">
+      <c r="F11194" s="7">
         <v>214.27</v>
       </c>
-      <c r="G183" s="7">
+      <c r="G11194" s="7">
         <v>105.54</v>
       </c>
-      <c r="H183" s="7">
+      <c r="H11194" s="7">
         <v>90.28</v>
       </c>
     </row>
     <row r="11195" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A184" s="5" t="s">
+      <c r="A11195" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B11195" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C184" s="14">
+      <c r="C11195" s="14">
         <v>10001</v>
       </c>
-      <c r="D184" s="5">
+      <c r="D11195" s="5">
         <v>1995</v>
       </c>
-      <c r="E184" s="7">
+      <c r="E11195" s="7">
         <v>0.54</v>
       </c>
-      <c r="F184" s="7">
+      <c r="F11195" s="7">
         <v>215.42</v>
       </c>
-      <c r="G184" s="7">
+      <c r="G11195" s="7">
         <v>106.11</v>
       </c>
-      <c r="H184" s="7">
+      <c r="H11195" s="7">
         <v>90.77</v>
       </c>
     </row>
     <row r="11196" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A185" s="5" t="s">
+      <c r="A11196" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B11196" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C185" s="14">
+      <c r="C11196" s="14">
         <v>10001</v>
       </c>
-      <c r="D185" s="5">
+      <c r="D11196" s="5">
         <v>1996</v>
       </c>
-      <c r="E185" s="7">
+      <c r="E11196" s="7">
         <v>1.65</v>
       </c>
-      <c r="F185" s="7">
+      <c r="F11196" s="7">
         <v>218.97</v>
       </c>
-      <c r="G185" s="7">
+      <c r="G11196" s="7">
         <v>107.85</v>
       </c>
-      <c r="H185" s="7">
+      <c r="H11196" s="7">
         <v>92.26</v>
       </c>
     </row>
     <row r="11197" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A186" s="5" t="s">
+      <c r="A11197" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B11197" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C186" s="14">
+      <c r="C11197" s="14">
         <v>10001</v>
       </c>
-      <c r="D186" s="5">
+      <c r="D11197" s="5">
         <v>1997</v>
       </c>
-      <c r="E186" s="7">
+      <c r="E11197" s="7">
         <v>3.45</v>
       </c>
-      <c r="F186" s="7">
+      <c r="F11197" s="7">
         <v>226.52</v>
       </c>
-      <c r="G186" s="7">
+      <c r="G11197" s="7">
         <v>111.57</v>
       </c>
-      <c r="H186" s="7">
+      <c r="H11197" s="7">
         <v>95.44</v>
       </c>
     </row>
     <row r="11198" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A187" s="5" t="s">
+      <c r="A11198" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B11198" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C187" s="14">
+      <c r="C11198" s="14">
         <v>10001</v>
       </c>
-      <c r="D187" s="5">
+      <c r="D11198" s="5">
         <v>1998</v>
       </c>
-      <c r="E187" s="7">
+      <c r="E11198" s="7">
         <v>1.24</v>
       </c>
-      <c r="F187" s="7">
+      <c r="F11198" s="7">
         <v>229.32</v>
       </c>
-      <c r="G187" s="7">
+      <c r="G11198" s="7">
         <v>112.95</v>
       </c>
-      <c r="H187" s="7">
+      <c r="H11198" s="7">
         <v>96.62</v>
       </c>
     </row>
     <row r="11199" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A188" s="5" t="s">
+      <c r="A11199" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B11199" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C188" s="14">
+      <c r="C11199" s="14">
         <v>10001</v>
       </c>
-      <c r="D188" s="5">
+      <c r="D11199" s="5">
         <v>1999</v>
       </c>
-      <c r="E188" s="7">
+      <c r="E11199" s="7">
         <v>1.19</v>
       </c>
-      <c r="F188" s="7">
+      <c r="F11199" s="7">
         <v>232.04</v>
       </c>
-      <c r="G188" s="7">
+      <c r="G11199" s="7">
         <v>114.29</v>
       </c>
-      <c r="H188" s="7">
+      <c r="H11199" s="7">
         <v>97.77</v>
       </c>
     </row>
     <row r="11200" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A189" s="5" t="s">
+      <c r="A11200" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B11200" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C189" s="14">
+      <c r="C11200" s="14">
         <v>10001</v>
       </c>
-      <c r="D189" s="5">
+      <c r="D11200" s="5">
         <v>2000</v>
       </c>
-      <c r="E189" s="7">
+      <c r="E11200" s="7">
         <v>2.29</v>
       </c>
-      <c r="F189" s="7">
+      <c r="F11200" s="7">
         <v>237.34</v>
       </c>
-      <c r="G189" s="7">
+      <c r="G11200" s="7">
         <v>116.9</v>
       </c>
-      <c r="H189" s="7">
+      <c r="H11200" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="11201" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A190" s="5" t="s">
+      <c r="A11201" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="B11201" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C190" s="14">
+      <c r="C11201" s="14">
         <v>10001</v>
       </c>
-      <c r="D190" s="5">
+      <c r="D11201" s="5">
         <v>2001</v>
       </c>
-      <c r="E190" s="7">
+      <c r="E11201" s="7">
         <v>6.21</v>
       </c>
-      <c r="F190" s="7">
+      <c r="F11201" s="7">
         <v>252.08</v>
       </c>
-      <c r="G190" s="7">
+      <c r="G11201" s="7">
         <v>124.16</v>
       </c>
-      <c r="H190" s="7">
+      <c r="H11201" s="7">
         <v>106.21</v>
       </c>
     </row>
     <row r="11202" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A191" s="5" t="s">
+      <c r="A11202" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="B11202" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C191" s="14">
+      <c r="C11202" s="14">
         <v>10001</v>
       </c>
-      <c r="D191" s="5">
+      <c r="D11202" s="5">
         <v>2002</v>
       </c>
-      <c r="E191" s="7">
+      <c r="E11202" s="7">
         <v>4.75</v>
       </c>
-      <c r="F191" s="7">
+      <c r="F11202" s="7">
         <v>264.06</v>
       </c>
-      <c r="G191" s="7">
+      <c r="G11202" s="7">
         <v>130.06</v>
       </c>
-      <c r="H191" s="7">
+      <c r="H11202" s="7">
         <v>111.26</v>
       </c>
     </row>
     <row r="11203" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A192" s="5" t="s">
+      <c r="A11203" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="B11203" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C192" s="14">
+      <c r="C11203" s="14">
         <v>10001</v>
       </c>
-      <c r="D192" s="5">
+      <c r="D11203" s="5">
         <v>2003</v>
       </c>
-      <c r="E192" s="7">
+      <c r="E11203" s="7">
         <v>4.2699999999999996</v>
       </c>
-      <c r="F192" s="7">
+      <c r="F11203" s="7">
         <v>275.33</v>
       </c>
-      <c r="G192" s="7">
+      <c r="G11203" s="7">
         <v>135.61000000000001</v>
       </c>
-      <c r="H192" s="7">
+      <c r="H11203" s="7">
         <v>116.01</v>
       </c>
     </row>
     <row r="11204" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A193" s="5" t="s">
+      <c r="A11204" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="B11204" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C193" s="14">
+      <c r="C11204" s="14">
         <v>10001</v>
       </c>
-      <c r="D193" s="5">
+      <c r="D11204" s="5">
         <v>2004</v>
       </c>
-      <c r="E193" s="7">
+      <c r="E11204" s="7">
         <v>12.34</v>
       </c>
-      <c r="F193" s="7">
+      <c r="F11204" s="7">
         <v>309.3</v>
       </c>
-      <c r="G193" s="7">
+      <c r="G11204" s="7">
         <v>152.35</v>
       </c>
-      <c r="H193" s="7">
+      <c r="H11204" s="7">
         <v>130.32</v>
       </c>
     </row>
     <row r="11205" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A194" s="5" t="s">
+      <c r="A11205" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B11205" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C194" s="14">
+      <c r="C11205" s="14">
         <v>10001</v>
       </c>
-      <c r="D194" s="5">
+      <c r="D11205" s="5">
         <v>2005</v>
       </c>
-      <c r="E194" s="7">
+      <c r="E11205" s="7">
         <v>18.149999999999999</v>
       </c>
-      <c r="F194" s="7">
+      <c r="F11205" s="7">
         <v>365.44</v>
       </c>
-      <c r="G194" s="7">
+      <c r="G11205" s="7">
         <v>179.99</v>
       </c>
-      <c r="H194" s="7">
+      <c r="H11205" s="7">
         <v>153.97</v>
       </c>
     </row>
     <row r="11206" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A195" s="5" t="s">
+      <c r="A11206" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B195" s="5" t="s">
+      <c r="B11206" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C195" s="14">
+      <c r="C11206" s="14">
         <v>10001</v>
       </c>
-      <c r="D195" s="5">
+      <c r="D11206" s="5">
         <v>2006</v>
       </c>
-      <c r="E195" s="7">
+      <c r="E11206" s="7">
         <v>11.11</v>
       </c>
-      <c r="F195" s="7">
+      <c r="F11206" s="7">
         <v>406.05</v>
       </c>
-      <c r="G195" s="7">
+      <c r="G11206" s="7">
         <v>200</v>
       </c>
-      <c r="H195" s="7">
+      <c r="H11206" s="7">
         <v>171.08</v>
       </c>
     </row>
     <row r="11207" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A196" s="5" t="s">
+      <c r="A11207" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B11207" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C196" s="14">
+      <c r="C11207" s="14">
         <v>10001</v>
       </c>
-      <c r="D196" s="5">
+      <c r="D11207" s="5">
         <v>2007</v>
       </c>
-      <c r="E196" s="7">
+      <c r="E11207" s="7">
         <v>3.93</v>
       </c>
-      <c r="F196" s="7">
+      <c r="F11207" s="7">
         <v>422.02</v>
       </c>
-      <c r="G196" s="7">
+      <c r="G11207" s="7">
         <v>207.86</v>
       </c>
-      <c r="H196" s="7">
+      <c r="H11207" s="7">
         <v>177.81</v>
       </c>
     </row>
     <row r="11208" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A197" s="5" t="s">
+      <c r="A11208" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B11208" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C197" s="14">
+      <c r="C11208" s="14">
         <v>10001</v>
       </c>
-      <c r="D197" s="5">
+      <c r="D11208" s="5">
         <v>2008</v>
       </c>
-      <c r="E197" s="7">
+      <c r="E11208" s="7">
         <v>-2.39</v>
       </c>
-      <c r="F197" s="7">
+      <c r="F11208" s="7">
         <v>411.93</v>
       </c>
-      <c r="G197" s="7">
+      <c r="G11208" s="7">
         <v>202.9</v>
       </c>
-      <c r="H197" s="7">
+      <c r="H11208" s="7">
         <v>173.56</v>
       </c>
     </row>
     <row r="11209" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A198" s="5" t="s">
+      <c r="A11209" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B11209" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C198" s="14">
+      <c r="C11209" s="14">
         <v>10001</v>
       </c>
-      <c r="D198" s="5">
+      <c r="D11209" s="5">
         <v>2009</v>
       </c>
-      <c r="E198" s="7">
+      <c r="E11209" s="7">
         <v>-8.25</v>
       </c>
-      <c r="F198" s="7">
+      <c r="F11209" s="7">
         <v>377.93</v>
       </c>
-      <c r="G198" s="7">
+      <c r="G11209" s="7">
         <v>186.15</v>
       </c>
-      <c r="H198" s="7">
+      <c r="H11209" s="7">
         <v>159.22999999999999</v>
       </c>
     </row>
     <row r="11210" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A199" s="5" t="s">
+      <c r="A11210" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B199" s="5" t="s">
+      <c r="B11210" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C199" s="14">
+      <c r="C11210" s="14">
         <v>10001</v>
       </c>
-      <c r="D199" s="5">
+      <c r="D11210" s="5">
         <v>2010</v>
       </c>
-      <c r="E199" s="7">
+      <c r="E11210" s="7">
         <v>-7.07</v>
       </c>
-      <c r="F199" s="7">
+      <c r="F11210" s="7">
         <v>351.2</v>
       </c>
-      <c r="G199" s="7">
+      <c r="G11210" s="7">
         <v>172.98</v>
       </c>
-      <c r="H199" s="7">
+      <c r="H11210" s="7">
         <v>147.97</v>
       </c>
     </row>
     <row r="11211" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A200" s="5" t="s">
+      <c r="A11211" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B11211" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C200" s="14">
+      <c r="C11211" s="14">
         <v>10001</v>
       </c>
-      <c r="D200" s="5">
+      <c r="D11211" s="5">
         <v>2011</v>
       </c>
-      <c r="E200" s="7">
+      <c r="E11211" s="7">
         <v>-5.27</v>
       </c>
-      <c r="F200" s="7">
+      <c r="F11211" s="7">
         <v>332.69</v>
       </c>
-      <c r="G200" s="7">
+      <c r="G11211" s="7">
         <v>163.87</v>
       </c>
-      <c r="H200" s="7">
+      <c r="H11211" s="7">
         <v>140.18</v>
       </c>
     </row>
     <row r="11212" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A201" s="5" t="s">
+      <c r="A11212" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="B11212" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C201" s="14">
+      <c r="C11212" s="14">
         <v>10001</v>
       </c>
-      <c r="D201" s="5">
+      <c r="D11212" s="5">
         <v>2012</v>
       </c>
-      <c r="E201" s="7">
+      <c r="E11212" s="7">
         <v>-3.17</v>
       </c>
-      <c r="F201" s="7">
+      <c r="F11212" s="7">
         <v>322.14</v>
       </c>
-      <c r="G201" s="7">
+      <c r="G11212" s="7">
         <v>158.66999999999999</v>
       </c>
-      <c r="H201" s="7">
+      <c r="H11212" s="7">
         <v>135.72999999999999</v>
       </c>
     </row>
     <row r="11213" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A202" s="5" t="s">
+      <c r="A11213" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B11213" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C202" s="14">
+      <c r="C11213" s="14">
         <v>10001</v>
       </c>
-      <c r="D202" s="5">
+      <c r="D11213" s="5">
         <v>2013</v>
       </c>
-      <c r="E202" s="7">
+      <c r="E11213" s="7">
         <v>0.24</v>
       </c>
-      <c r="F202" s="7">
+      <c r="F11213" s="7">
         <v>322.92</v>
       </c>
-      <c r="G202" s="7">
+      <c r="G11213" s="7">
         <v>159.06</v>
       </c>
-      <c r="H202" s="7">
+      <c r="H11213" s="7">
         <v>136.06</v>
       </c>
     </row>
     <row r="11214" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A203" s="5" t="s">
+      <c r="A11214" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B203" s="5" t="s">
+      <c r="B11214" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C203" s="14">
+      <c r="C11214" s="14">
         <v>10001</v>
       </c>
-      <c r="D203" s="5">
+      <c r="D11214" s="5">
         <v>2014</v>
       </c>
-      <c r="E203" s="7">
+      <c r="E11214" s="7">
         <v>2.1800000000000002</v>
       </c>
-      <c r="F203" s="7">
+      <c r="F11214" s="7">
         <v>329.98</v>
       </c>
-      <c r="G203" s="7">
+      <c r="G11214" s="7">
         <v>162.53</v>
       </c>
-      <c r="H203" s="7">
+      <c r="H11214" s="7">
         <v>139.03</v>
       </c>
     </row>
     <row r="11215" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A204" s="5" t="s">
+      <c r="A11215" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B11215" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C204" s="14">
+      <c r="C11215" s="14">
         <v>10001</v>
       </c>
-      <c r="D204" s="5">
+      <c r="D11215" s="5">
         <v>2015</v>
       </c>
-      <c r="E204" s="7">
+      <c r="E11215" s="7">
         <v>2.66</v>
       </c>
-      <c r="F204" s="7">
+      <c r="F11215" s="7">
         <v>338.77</v>
       </c>
-      <c r="G204" s="7">
+      <c r="G11215" s="7">
         <v>166.86</v>
       </c>
-      <c r="H204" s="7">
+      <c r="H11215" s="7">
         <v>142.72999999999999</v>
       </c>
     </row>
     <row r="11216" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A205" s="5" t="s">
+      <c r="A11216" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B205" s="5" t="s">
+      <c r="B11216" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C205" s="14">
+      <c r="C11216" s="14">
         <v>10001</v>
       </c>
-      <c r="D205" s="5">
+      <c r="D11216" s="5">
         <v>2016</v>
       </c>
-      <c r="E205" s="7">
+      <c r="E11216" s="7">
         <v>4.41</v>
       </c>
-      <c r="F205" s="7">
+      <c r="F11216" s="7">
         <v>353.7</v>
       </c>
-      <c r="G205" s="7">
+      <c r="G11216" s="7">
         <v>174.21</v>
       </c>
-      <c r="H205" s="7">
+      <c r="H11216" s="7">
         <v>149.03</v>
       </c>
     </row>
     <row r="11217" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A206" s="5" t="s">
+      <c r="A11217" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B11217" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C206" s="14">
+      <c r="C11217" s="14">
         <v>10001</v>
       </c>
-      <c r="D206" s="5">
+      <c r="D11217" s="5">
         <v>2017</v>
       </c>
-      <c r="E206" s="7">
+      <c r="E11217" s="7">
         <v>0.97</v>
       </c>
-      <c r="F206" s="7">
+      <c r="F11217" s="7">
         <v>357.11</v>
       </c>
-      <c r="G206" s="7">
+      <c r="G11217" s="7">
         <v>175.9</v>
       </c>
-      <c r="H206" s="7">
+      <c r="H11217" s="7">
         <v>150.46</v>
       </c>
     </row>
     <row r="11218" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A207" s="5" t="s">
+      <c r="A11218" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B11218" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C207" s="14">
+      <c r="C11218" s="14">
         <v>10001</v>
       </c>
-      <c r="D207" s="5">
+      <c r="D11218" s="5">
         <v>2018</v>
       </c>
-      <c r="E207" s="7">
+      <c r="E11218" s="7">
         <v>4.82</v>
       </c>
-      <c r="F207" s="7">
+      <c r="F11218" s="7">
         <v>374.33</v>
       </c>
-      <c r="G207" s="7">
+      <c r="G11218" s="7">
         <v>184.37</v>
       </c>
-      <c r="H207" s="7">
+      <c r="H11218" s="7">
         <v>157.72</v>
       </c>
     </row>
     <row r="11219" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A208" s="5" t="s">
+      <c r="A11219" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B11219" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C208" s="14">
+      <c r="C11219" s="14">
         <v>10001</v>
       </c>
-      <c r="D208" s="5">
+      <c r="D11219" s="5">
         <v>2019</v>
       </c>
-      <c r="E208" s="7">
+      <c r="E11219" s="7">
         <v>2.46</v>
       </c>
-      <c r="F208" s="7">
+      <c r="F11219" s="7">
         <v>383.55</v>
       </c>
-      <c r="G208" s="7">
+      <c r="G11219" s="7">
         <v>188.92</v>
       </c>
-      <c r="H208" s="7">
+      <c r="H11219" s="7">
         <v>161.6</v>
       </c>
     </row>
     <row r="11220" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A209" s="5" t="s">
+      <c r="A11220" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B209" s="5" t="s">
+      <c r="B11220" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C209" s="14">
+      <c r="C11220" s="14">
         <v>10001</v>
       </c>
-      <c r="D209" s="5">
+      <c r="D11220" s="5">
         <v>2020</v>
       </c>
-      <c r="E209" s="7">
+      <c r="E11220" s="7">
         <v>5.0599999999999996</v>
       </c>
-      <c r="F209" s="7">
+      <c r="F11220" s="7">
         <v>402.94</v>
       </c>
-      <c r="G209" s="7">
+      <c r="G11220" s="7">
         <v>198.47</v>
       </c>
-      <c r="H209" s="7">
+      <c r="H11220" s="7">
         <v>169.77</v>
       </c>
     </row>
     <row r="11221" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A210" s="5" t="s">
+      <c r="A11221" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B11221" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C210" s="14">
+      <c r="C11221" s="14">
         <v>10001</v>
       </c>
-      <c r="D210" s="5">
+      <c r="D11221" s="5">
         <v>2021</v>
       </c>
-      <c r="E210" s="7">
+      <c r="E11221" s="7">
         <v>11.96</v>
       </c>
-      <c r="F210" s="7">
+      <c r="F11221" s="7">
         <v>451.13</v>
       </c>
-      <c r="G210" s="7">
+      <c r="G11221" s="7">
         <v>222.2</v>
       </c>
-      <c r="H210" s="7">
+      <c r="H11221" s="7">
         <v>190.08</v>
       </c>
     </row>
     <row r="11222" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A211" s="5" t="s">
+      <c r="A11222" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="B11222" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C211" s="14">
+      <c r="C11222" s="14">
         <v>10001</v>
       </c>
-      <c r="D211" s="5">
+      <c r="D11222" s="5">
         <v>2022</v>
       </c>
-      <c r="E211" s="7">
+      <c r="E11222" s="7">
         <v>15.88</v>
       </c>
-      <c r="F211" s="7">
+      <c r="F11222" s="7">
         <v>522.75</v>
       </c>
-      <c r="G211" s="7">
+      <c r="G11222" s="7">
         <v>257.48</v>
       </c>
-      <c r="H211" s="7">
+      <c r="H11222" s="7">
         <v>220.25</v>
       </c>
     </row>
     <row r="11223" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A212" s="5" t="s">
+      <c r="A11223" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B11223" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C212" s="14">
+      <c r="C11223" s="14">
         <v>10001</v>
       </c>
-      <c r="D212" s="5">
+      <c r="D11223" s="5">
         <v>2023</v>
       </c>
-      <c r="E212" s="7">
+      <c r="E11223" s="7">
         <v>6.02</v>
       </c>
-      <c r="F212" s="7">
+      <c r="F11223" s="7">
         <v>554.21</v>
       </c>
-      <c r="G212" s="7">
+      <c r="G11223" s="7">
         <v>272.97000000000003</v>
       </c>
-      <c r="H212" s="7">
+      <c r="H11223" s="7">
         <v>233.51</v>
       </c>
     </row>
     <row r="11224" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A213" s="5" t="s">
+      <c r="A11224" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B11224" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C213" s="14">
+      <c r="C11224" s="14">
         <v>10001</v>
       </c>
-      <c r="D213" s="5">
+      <c r="D11224" s="5">
         <v>2024</v>
       </c>
-      <c r="E213" s="7">
+      <c r="E11224" s="7">
         <v>5.62</v>
       </c>
-      <c r="F213" s="7">
+      <c r="F11224" s="7">
         <v>585.34</v>
       </c>
-      <c r="G213" s="7">
+      <c r="G11224" s="7">
         <v>288.31</v>
       </c>
-      <c r="H213" s="7">
+      <c r="H11224" s="7">
         <v>246.62</v>
       </c>
     </row>
     <row r="11225" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A214" s="5" t="s">
+      <c r="A11225" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B11225" s="5" t="s">
         <v>1091</v>
       </c>
-      <c r="C214" s="14">
+      <c r="C11225" s="14">
         <v>10001</v>
       </c>
-      <c r="D214" s="5">
+      <c r="D11225" s="5">
         <v>2025</v>
       </c>
-      <c r="E214" s="7">
+      <c r="E11225" s="7">
         <v>2.5299999999999998</v>
       </c>
-      <c r="F214" s="7">
+      <c r="F11225" s="7">
         <v>600.16999999999996</v>
       </c>
-      <c r="G214" s="7">
+      <c r="G11225" s="7">
         <v>295.61</v>
       </c>
-      <c r="H214" s="7">
+      <c r="H11225" s="7">
         <v>252.87</v>
       </c>
     </row>
     <row r="11226" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A215" s="5" t="s">
+      <c r="A11226" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B215" s="5" t="s">
+      <c r="B11226" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C215" s="14">
+      <c r="C11226" s="14">
         <v>10003</v>
       </c>
-      <c r="D215" s="5">
+      <c r="D11226" s="5">
         <v>1975</v>
       </c>
-      <c r="F215" s="7">
+      <c r="F11226" s="7">
         <v>100</v>
       </c>
-      <c r="G215" s="7">
+      <c r="G11226" s="7">
         <v>33.6</v>
       </c>
-      <c r="H215" s="7">
+      <c r="H11226" s="7">
         <v>29.18</v>
       </c>
     </row>
     <row r="11227" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A216" s="5" t="s">
+      <c r="A11227" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="B11227" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C216" s="14">
+      <c r="C11227" s="14">
         <v>10003</v>
       </c>
-      <c r="D216" s="5">
+      <c r="D11227" s="5">
         <v>1976</v>
       </c>
-      <c r="E216" s="7">
+      <c r="E11227" s="7">
         <v>7.91</v>
       </c>
-      <c r="F216" s="7">
+      <c r="F11227" s="7">
         <v>107.91</v>
       </c>
-      <c r="G216" s="7">
+      <c r="G11227" s="7">
         <v>36.25</v>
       </c>
-      <c r="H216" s="7">
+      <c r="H11227" s="7">
         <v>31.49</v>
       </c>
     </row>
     <row r="11228" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A217" s="5" t="s">
+      <c r="A11228" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B217" s="5" t="s">
+      <c r="B11228" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C217" s="14">
+      <c r="C11228" s="14">
         <v>10003</v>
       </c>
-      <c r="D217" s="5">
+      <c r="D11228" s="5">
         <v>1977</v>
       </c>
-      <c r="E217" s="7">
+      <c r="E11228" s="7">
         <v>-2.98</v>
       </c>
-      <c r="F217" s="7">
+      <c r="F11228" s="7">
         <v>104.69</v>
       </c>
-      <c r="G217" s="7">
+      <c r="G11228" s="7">
         <v>35.17</v>
       </c>
-      <c r="H217" s="7">
+      <c r="H11228" s="7">
         <v>30.55</v>
       </c>
     </row>
     <row r="11229" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A218" s="5" t="s">
+      <c r="A11229" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B218" s="5" t="s">
+      <c r="B11229" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C218" s="14">
+      <c r="C11229" s="14">
         <v>10003</v>
       </c>
-      <c r="D218" s="5">
+      <c r="D11229" s="5">
         <v>1978</v>
       </c>
-      <c r="E218" s="7">
+      <c r="E11229" s="7">
         <v>6.45</v>
       </c>
-      <c r="F218" s="7">
+      <c r="F11229" s="7">
         <v>111.45</v>
       </c>
-      <c r="G218" s="7">
+      <c r="G11229" s="7">
         <v>37.44</v>
       </c>
-      <c r="H218" s="7">
+      <c r="H11229" s="7">
         <v>32.520000000000003</v>
       </c>
     </row>
     <row r="11230" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A219" s="5" t="s">
+      <c r="A11230" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B11230" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C219" s="14">
+      <c r="C11230" s="14">
         <v>10003</v>
       </c>
-      <c r="D219" s="5">
+      <c r="D11230" s="5">
         <v>1979</v>
       </c>
-      <c r="E219" s="7">
+      <c r="E11230" s="7">
         <v>6.58</v>
       </c>
-      <c r="F219" s="7">
+      <c r="F11230" s="7">
         <v>118.78</v>
       </c>
-      <c r="G219" s="7">
+      <c r="G11230" s="7">
         <v>39.909999999999997</v>
       </c>
-      <c r="H219" s="7">
+      <c r="H11230" s="7">
         <v>34.659999999999997</v>
       </c>
     </row>
     <row r="11231" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A220" s="5" t="s">
+      <c r="A11231" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="B11231" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C220" s="14">
+      <c r="C11231" s="14">
         <v>10003</v>
       </c>
-      <c r="D220" s="5">
+      <c r="D11231" s="5">
         <v>1980</v>
       </c>
-      <c r="E220" s="7">
+      <c r="E11231" s="7">
         <v>16.88</v>
       </c>
-      <c r="F220" s="7">
+      <c r="F11231" s="7">
         <v>138.83000000000001</v>
       </c>
-      <c r="G220" s="7">
+      <c r="G11231" s="7">
         <v>46.64</v>
       </c>
-      <c r="H220" s="7">
+      <c r="H11231" s="7">
         <v>40.51</v>
       </c>
     </row>
     <row r="11232" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A221" s="5" t="s">
+      <c r="A11232" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B11232" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C221" s="14">
+      <c r="C11232" s="14">
         <v>10003</v>
       </c>
-      <c r="D221" s="5">
+      <c r="D11232" s="5">
         <v>1981</v>
       </c>
-      <c r="E221" s="7">
+      <c r="E11232" s="7">
         <v>7.19</v>
       </c>
-      <c r="F221" s="7">
+      <c r="F11232" s="7">
         <v>148.82</v>
       </c>
-      <c r="G221" s="7">
+      <c r="G11232" s="7">
         <v>50</v>
       </c>
-      <c r="H221" s="7">
+      <c r="H11232" s="7">
         <v>43.42</v>
       </c>
     </row>
     <row r="11233" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A222" s="5" t="s">
+      <c r="A11233" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="B11233" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C222" s="14">
+      <c r="C11233" s="14">
         <v>10003</v>
       </c>
-      <c r="D222" s="5">
+      <c r="D11233" s="5">
         <v>1982</v>
       </c>
-      <c r="E222" s="7">
+      <c r="E11233" s="7">
         <v>2.63</v>
       </c>
-      <c r="F222" s="7">
+      <c r="F11233" s="7">
         <v>152.72999999999999</v>
       </c>
-      <c r="G222" s="7">
+      <c r="G11233" s="7">
         <v>51.31</v>
       </c>
-      <c r="H222" s="7">
+      <c r="H11233" s="7">
         <v>44.56</v>
       </c>
     </row>
     <row r="11234" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A223" s="5" t="s">
+      <c r="A11234" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B223" s="5" t="s">
+      <c r="B11234" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C223" s="14">
+      <c r="C11234" s="14">
         <v>10003</v>
       </c>
-      <c r="D223" s="5">
+      <c r="D11234" s="5">
         <v>1983</v>
       </c>
-      <c r="E223" s="7">
+      <c r="E11234" s="7">
         <v>6.01</v>
       </c>
-      <c r="F223" s="7">
+      <c r="F11234" s="7">
         <v>161.91</v>
       </c>
-      <c r="G223" s="7">
+      <c r="G11234" s="7">
         <v>54.4</v>
       </c>
-      <c r="H223" s="7">
+      <c r="H11234" s="7">
         <v>47.24</v>
       </c>
     </row>
     <row r="11235" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A224" s="5" t="s">
+      <c r="A11235" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B224" s="5" t="s">
+      <c r="B11235" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C224" s="14">
+      <c r="C11235" s="14">
         <v>10003</v>
       </c>
-      <c r="D224" s="5">
+      <c r="D11235" s="5">
         <v>1984</v>
       </c>
-      <c r="E224" s="7">
+      <c r="E11235" s="7">
         <v>8.9600000000000009</v>
       </c>
-      <c r="F224" s="7">
+      <c r="F11235" s="7">
         <v>176.41</v>
       </c>
-      <c r="G224" s="7">
+      <c r="G11235" s="7">
         <v>59.27</v>
       </c>
-      <c r="H224" s="7">
+      <c r="H11235" s="7">
         <v>51.47</v>
       </c>
     </row>
     <row r="11236" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A225" s="5" t="s">
+      <c r="A11236" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B11236" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C225" s="14">
+      <c r="C11236" s="14">
         <v>10003</v>
       </c>
-      <c r="D225" s="5">
+      <c r="D11236" s="5">
         <v>1985</v>
       </c>
-      <c r="E225" s="7">
+      <c r="E11236" s="7">
         <v>7.71</v>
       </c>
-      <c r="F225" s="7">
+      <c r="F11236" s="7">
         <v>190.01</v>
       </c>
-      <c r="G225" s="7">
+      <c r="G11236" s="7">
         <v>63.84</v>
       </c>
-      <c r="H225" s="7">
+      <c r="H11236" s="7">
         <v>55.44</v>
       </c>
     </row>
     <row r="11237" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A226" s="5" t="s">
+      <c r="A11237" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B11237" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C226" s="14">
+      <c r="C11237" s="14">
         <v>10003</v>
       </c>
-      <c r="D226" s="5">
+      <c r="D11237" s="5">
         <v>1986</v>
       </c>
-      <c r="E226" s="7">
+      <c r="E11237" s="7">
         <v>10.220000000000001</v>
       </c>
-      <c r="F226" s="7">
+      <c r="F11237" s="7">
         <v>209.43</v>
       </c>
-      <c r="G226" s="7">
+      <c r="G11237" s="7">
         <v>70.36</v>
       </c>
-      <c r="H226" s="7">
+      <c r="H11237" s="7">
         <v>61.11</v>
       </c>
     </row>
     <row r="11238" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A227" s="5" t="s">
+      <c r="A11238" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B11238" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C227" s="14">
+      <c r="C11238" s="14">
         <v>10003</v>
       </c>
-      <c r="D227" s="5">
+      <c r="D11238" s="5">
         <v>1987</v>
       </c>
-      <c r="E227" s="7">
+      <c r="E11238" s="7">
         <v>11.91</v>
       </c>
-      <c r="F227" s="7">
+      <c r="F11238" s="7">
         <v>234.37</v>
       </c>
-      <c r="G227" s="7">
+      <c r="G11238" s="7">
         <v>78.739999999999995</v>
       </c>
-      <c r="H227" s="7">
+      <c r="H11238" s="7">
         <v>68.39</v>
       </c>
     </row>
     <row r="11239" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A228" s="5" t="s">
+      <c r="A11239" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B11239" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C228" s="14">
+      <c r="C11239" s="14">
         <v>10003</v>
       </c>
-      <c r="D228" s="5">
+      <c r="D11239" s="5">
         <v>1988</v>
       </c>
-      <c r="E228" s="7">
+      <c r="E11239" s="7">
         <v>12.74</v>
       </c>
-      <c r="F228" s="7">
+      <c r="F11239" s="7">
         <v>264.24</v>
       </c>
-      <c r="G228" s="7">
+      <c r="G11239" s="7">
         <v>88.78</v>
       </c>
-      <c r="H228" s="7">
+      <c r="H11239" s="7">
         <v>77.099999999999994</v>
       </c>
     </row>
     <row r="11240" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A229" s="5" t="s">
+      <c r="A11240" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B11240" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C229" s="14">
+      <c r="C11240" s="14">
         <v>10003</v>
       </c>
-      <c r="D229" s="5">
+      <c r="D11240" s="5">
         <v>1989</v>
       </c>
-      <c r="E229" s="7">
+      <c r="E11240" s="7">
         <v>10</v>
       </c>
-      <c r="F229" s="7">
+      <c r="F11240" s="7">
         <v>290.67</v>
       </c>
-      <c r="G229" s="7">
+      <c r="G11240" s="7">
         <v>97.66</v>
       </c>
-      <c r="H229" s="7">
+      <c r="H11240" s="7">
         <v>84.81</v>
       </c>
     </row>
     <row r="11241" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A230" s="5" t="s">
+      <c r="A11241" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B11241" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C230" s="14">
+      <c r="C11241" s="14">
         <v>10003</v>
       </c>
-      <c r="D230" s="5">
+      <c r="D11241" s="5">
         <v>1990</v>
       </c>
-      <c r="E230" s="7">
+      <c r="E11241" s="7">
         <v>2.4</v>
       </c>
-      <c r="F230" s="7">
+      <c r="F11241" s="7">
         <v>297.64</v>
       </c>
-      <c r="G230" s="7">
+      <c r="G11241" s="7">
         <v>100</v>
       </c>
-      <c r="H230" s="7">
+      <c r="H11241" s="7">
         <v>86.85</v>
       </c>
     </row>
     <row r="11242" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A231" s="5" t="s">
+      <c r="A11242" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B11242" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C231" s="14">
+      <c r="C11242" s="14">
         <v>10003</v>
       </c>
-      <c r="D231" s="5">
+      <c r="D11242" s="5">
         <v>1991</v>
       </c>
-      <c r="E231" s="7">
+      <c r="E11242" s="7">
         <v>1.1100000000000001</v>
       </c>
-      <c r="F231" s="7">
+      <c r="F11242" s="7">
         <v>300.93</v>
       </c>
-      <c r="G231" s="7">
+      <c r="G11242" s="7">
         <v>101.11</v>
       </c>
-      <c r="H231" s="7">
+      <c r="H11242" s="7">
         <v>87.81</v>
       </c>
     </row>
     <row r="11243" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A232" s="5" t="s">
+      <c r="A11243" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B11243" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C232" s="14">
+      <c r="C11243" s="14">
         <v>10003</v>
       </c>
-      <c r="D232" s="5">
+      <c r="D11243" s="5">
         <v>1992</v>
       </c>
-      <c r="E232" s="7">
+      <c r="E11243" s="7">
         <v>0.31</v>
       </c>
-      <c r="F232" s="7">
+      <c r="F11243" s="7">
         <v>301.87</v>
       </c>
-      <c r="G232" s="7">
+      <c r="G11243" s="7">
         <v>101.42</v>
       </c>
-      <c r="H232" s="7">
+      <c r="H11243" s="7">
         <v>88.08</v>
       </c>
     </row>
     <row r="11244" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A233" s="5" t="s">
+      <c r="A11244" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B11244" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C233" s="14">
+      <c r="C11244" s="14">
         <v>10003</v>
       </c>
-      <c r="D233" s="5">
+      <c r="D11244" s="5">
         <v>1993</v>
       </c>
-      <c r="E233" s="7">
+      <c r="E11244" s="7">
         <v>-0.37</v>
       </c>
-      <c r="F233" s="7">
+      <c r="F11244" s="7">
         <v>300.74</v>
       </c>
-      <c r="G233" s="7">
+      <c r="G11244" s="7">
         <v>101.04</v>
       </c>
-      <c r="H233" s="7">
+      <c r="H11244" s="7">
         <v>87.75</v>
       </c>
     </row>
     <row r="11245" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A234" s="5" t="s">
+      <c r="A11245" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B234" s="5" t="s">
+      <c r="B11245" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C234" s="14">
+      <c r="C11245" s="14">
         <v>10003</v>
       </c>
-      <c r="D234" s="5">
+      <c r="D11245" s="5">
         <v>1994</v>
       </c>
-      <c r="E234" s="7">
+      <c r="E11245" s="7">
         <v>-1.23</v>
       </c>
-      <c r="F234" s="7">
+      <c r="F11245" s="7">
         <v>297.02</v>
       </c>
-      <c r="G234" s="7">
+      <c r="G11245" s="7">
         <v>99.79</v>
       </c>
-      <c r="H234" s="7">
+      <c r="H11245" s="7">
         <v>86.67</v>
       </c>
     </row>
     <row r="11246" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A235" s="5" t="s">
+      <c r="A11246" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B235" s="5" t="s">
+      <c r="B11246" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C235" s="14">
+      <c r="C11246" s="14">
         <v>10003</v>
       </c>
-      <c r="D235" s="5">
+      <c r="D11246" s="5">
         <v>1995</v>
       </c>
-      <c r="E235" s="7">
+      <c r="E11246" s="7">
         <v>-0.39</v>
       </c>
-      <c r="F235" s="7">
+      <c r="F11246" s="7">
         <v>295.87</v>
       </c>
-      <c r="G235" s="7">
+      <c r="G11246" s="7">
         <v>99.4</v>
       </c>
-      <c r="H235" s="7">
+      <c r="H11246" s="7">
         <v>86.33</v>
       </c>
     </row>
     <row r="11247" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A236" s="5" t="s">
+      <c r="A11247" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="B11247" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C236" s="14">
+      <c r="C11247" s="14">
         <v>10003</v>
       </c>
-      <c r="D236" s="5">
+      <c r="D11247" s="5">
         <v>1996</v>
       </c>
-      <c r="E236" s="7">
+      <c r="E11247" s="7">
         <v>1.52</v>
       </c>
-      <c r="F236" s="7">
+      <c r="F11247" s="7">
         <v>300.38</v>
       </c>
-      <c r="G236" s="7">
+      <c r="G11247" s="7">
         <v>100.92</v>
       </c>
-      <c r="H236" s="7">
+      <c r="H11247" s="7">
         <v>87.64</v>
       </c>
     </row>
     <row r="11248" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A237" s="5" t="s">
+      <c r="A11248" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B237" s="5" t="s">
+      <c r="B11248" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C237" s="14">
+      <c r="C11248" s="14">
         <v>10003</v>
       </c>
-      <c r="D237" s="5">
+      <c r="D11248" s="5">
         <v>1997</v>
       </c>
-      <c r="E237" s="7">
+      <c r="E11248" s="7">
         <v>1.23</v>
       </c>
-      <c r="F237" s="7">
+      <c r="F11248" s="7">
         <v>304.07</v>
       </c>
-      <c r="G237" s="7">
+      <c r="G11248" s="7">
         <v>102.16</v>
       </c>
-      <c r="H237" s="7">
+      <c r="H11248" s="7">
         <v>88.72</v>
       </c>
     </row>
     <row r="11249" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A238" s="5" t="s">
+      <c r="A11249" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B238" s="5" t="s">
+      <c r="B11249" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C238" s="14">
+      <c r="C11249" s="14">
         <v>10003</v>
       </c>
-      <c r="D238" s="5">
+      <c r="D11249" s="5">
         <v>1998</v>
       </c>
-      <c r="E238" s="7">
+      <c r="E11249" s="7">
         <v>2.85</v>
       </c>
-      <c r="F238" s="7">
+      <c r="F11249" s="7">
         <v>312.72000000000003</v>
       </c>
-      <c r="G238" s="7">
+      <c r="G11249" s="7">
         <v>105.07</v>
       </c>
-      <c r="H238" s="7">
+      <c r="H11249" s="7">
         <v>91.25</v>
       </c>
     </row>
     <row r="11250" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A239" s="5" t="s">
+      <c r="A11250" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B239" s="5" t="s">
+      <c r="B11250" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C239" s="14">
+      <c r="C11250" s="14">
         <v>10003</v>
       </c>
-      <c r="D239" s="5">
+      <c r="D11250" s="5">
         <v>1999</v>
       </c>
-      <c r="E239" s="7">
+      <c r="E11250" s="7">
         <v>3.17</v>
       </c>
-      <c r="F239" s="7">
+      <c r="F11250" s="7">
         <v>322.64</v>
       </c>
-      <c r="G239" s="7">
+      <c r="G11250" s="7">
         <v>108.4</v>
       </c>
-      <c r="H239" s="7">
+      <c r="H11250" s="7">
         <v>94.14</v>
       </c>
     </row>
     <row r="11251" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A240" s="5" t="s">
+      <c r="A11251" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="B11251" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C240" s="14">
+      <c r="C11251" s="14">
         <v>10003</v>
       </c>
-      <c r="D240" s="5">
+      <c r="D11251" s="5">
         <v>2000</v>
       </c>
-      <c r="E240" s="7">
+      <c r="E11251" s="7">
         <v>6.22</v>
       </c>
-      <c r="F240" s="7">
+      <c r="F11251" s="7">
         <v>342.72</v>
       </c>
-      <c r="G240" s="7">
+      <c r="G11251" s="7">
         <v>115.15</v>
       </c>
-      <c r="H240" s="7">
+      <c r="H11251" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="11252" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A241" s="5" t="s">
+      <c r="A11252" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B241" s="5" t="s">
+      <c r="B11252" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C241" s="14">
+      <c r="C11252" s="14">
         <v>10003</v>
       </c>
-      <c r="D241" s="5">
+      <c r="D11252" s="5">
         <v>2001</v>
       </c>
-      <c r="E241" s="7">
+      <c r="E11252" s="7">
         <v>6.64</v>
       </c>
-      <c r="F241" s="7">
+      <c r="F11252" s="7">
         <v>365.47</v>
       </c>
-      <c r="G241" s="7">
+      <c r="G11252" s="7">
         <v>122.79</v>
       </c>
-      <c r="H241" s="7">
+      <c r="H11252" s="7">
         <v>106.64</v>
       </c>
     </row>
     <row r="11253" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A242" s="5" t="s">
+      <c r="A11253" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="B11253" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C242" s="14">
+      <c r="C11253" s="14">
         <v>10003</v>
       </c>
-      <c r="D242" s="5">
+      <c r="D11253" s="5">
         <v>2002</v>
       </c>
-      <c r="E242" s="7">
+      <c r="E11253" s="7">
         <v>7.22</v>
       </c>
-      <c r="F242" s="7">
+      <c r="F11253" s="7">
         <v>391.87</v>
       </c>
-      <c r="G242" s="7">
+      <c r="G11253" s="7">
         <v>131.66</v>
       </c>
-      <c r="H242" s="7">
+      <c r="H11253" s="7">
         <v>114.34</v>
       </c>
     </row>
     <row r="11254" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A243" s="5" t="s">
+      <c r="A11254" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="B11254" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C243" s="14">
+      <c r="C11254" s="14">
         <v>10003</v>
       </c>
-      <c r="D243" s="5">
+      <c r="D11254" s="5">
         <v>2003</v>
       </c>
-      <c r="E243" s="7">
+      <c r="E11254" s="7">
         <v>6.74</v>
       </c>
-      <c r="F243" s="7">
+      <c r="F11254" s="7">
         <v>418.28</v>
       </c>
-      <c r="G243" s="7">
+      <c r="G11254" s="7">
         <v>140.53</v>
       </c>
-      <c r="H243" s="7">
+      <c r="H11254" s="7">
         <v>122.05</v>
       </c>
     </row>
     <row r="11255" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A244" s="5" t="s">
+      <c r="A11255" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B244" s="5" t="s">
+      <c r="B11255" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C244" s="14">
+      <c r="C11255" s="14">
         <v>10003</v>
       </c>
-      <c r="D244" s="5">
+      <c r="D11255" s="5">
         <v>2004</v>
       </c>
-      <c r="E244" s="7">
+      <c r="E11255" s="7">
         <v>12.99</v>
       </c>
-      <c r="F244" s="7">
+      <c r="F11255" s="7">
         <v>472.62</v>
       </c>
-      <c r="G244" s="7">
+      <c r="G11255" s="7">
         <v>158.79</v>
       </c>
-      <c r="H244" s="7">
+      <c r="H11255" s="7">
         <v>137.9</v>
       </c>
     </row>
     <row r="11256" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A245" s="5" t="s">
+      <c r="A11256" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B11256" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C245" s="14">
+      <c r="C11256" s="14">
         <v>10003</v>
       </c>
-      <c r="D245" s="5">
+      <c r="D11256" s="5">
         <v>2005</v>
       </c>
-      <c r="E245" s="7">
+      <c r="E11256" s="7">
         <v>15.31</v>
       </c>
-      <c r="F245" s="7">
+      <c r="F11256" s="7">
         <v>544.96</v>
       </c>
-      <c r="G245" s="7">
+      <c r="G11256" s="7">
         <v>183.09</v>
       </c>
-      <c r="H245" s="7">
+      <c r="H11256" s="7">
         <v>159.01</v>
       </c>
     </row>
     <row r="11257" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A246" s="5" t="s">
+      <c r="A11257" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B11257" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C246" s="14">
+      <c r="C11257" s="14">
         <v>10003</v>
       </c>
-      <c r="D246" s="5">
+      <c r="D11257" s="5">
         <v>2006</v>
       </c>
-      <c r="E246" s="7">
+      <c r="E11257" s="7">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F246" s="7">
+      <c r="F11257" s="7">
         <v>590.11</v>
       </c>
-      <c r="G246" s="7">
+      <c r="G11257" s="7">
         <v>198.26</v>
       </c>
-      <c r="H246" s="7">
+      <c r="H11257" s="7">
         <v>172.18</v>
       </c>
     </row>
     <row r="11258" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A247" s="5" t="s">
+      <c r="A11258" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B11258" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C247" s="14">
+      <c r="C11258" s="14">
         <v>10003</v>
       </c>
-      <c r="D247" s="5">
+      <c r="D11258" s="5">
         <v>2007</v>
       </c>
-      <c r="E247" s="7">
+      <c r="E11258" s="7">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F247" s="7">
+      <c r="F11258" s="7">
         <v>604.66</v>
       </c>
-      <c r="G247" s="7">
+      <c r="G11258" s="7">
         <v>203.15</v>
       </c>
-      <c r="H247" s="7">
+      <c r="H11258" s="7">
         <v>176.43</v>
       </c>
     </row>
     <row r="11259" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A248" s="5" t="s">
+      <c r="A11259" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B248" s="5" t="s">
+      <c r="B11259" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C248" s="14">
+      <c r="C11259" s="14">
         <v>10003</v>
       </c>
-      <c r="D248" s="5">
+      <c r="D11259" s="5">
         <v>2008</v>
       </c>
-      <c r="E248" s="7">
+      <c r="E11259" s="7">
         <v>-3.04</v>
       </c>
-      <c r="F248" s="7">
+      <c r="F11259" s="7">
         <v>586.28</v>
       </c>
-      <c r="G248" s="7">
+      <c r="G11259" s="7">
         <v>196.98</v>
       </c>
-      <c r="H248" s="7">
+      <c r="H11259" s="7">
         <v>171.07</v>
       </c>
     </row>
     <row r="11260" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A249" s="5" t="s">
+      <c r="A11260" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="B11260" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C249" s="14">
+      <c r="C11260" s="14">
         <v>10003</v>
       </c>
-      <c r="D249" s="5">
+      <c r="D11260" s="5">
         <v>2009</v>
       </c>
-      <c r="E249" s="7">
+      <c r="E11260" s="7">
         <v>-5.98</v>
       </c>
-      <c r="F249" s="7">
+      <c r="F11260" s="7">
         <v>551.20000000000005</v>
       </c>
-      <c r="G249" s="7">
+      <c r="G11260" s="7">
         <v>185.19</v>
       </c>
-      <c r="H249" s="7">
+      <c r="H11260" s="7">
         <v>160.83000000000001</v>
       </c>
     </row>
     <row r="11261" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A250" s="5" t="s">
+      <c r="A11261" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B250" s="5" t="s">
+      <c r="B11261" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C250" s="14">
+      <c r="C11261" s="14">
         <v>10003</v>
       </c>
-      <c r="D250" s="5">
+      <c r="D11261" s="5">
         <v>2010</v>
       </c>
-      <c r="E250" s="7">
+      <c r="E11261" s="7">
         <v>-4.12</v>
       </c>
-      <c r="F250" s="7">
+      <c r="F11261" s="7">
         <v>528.5</v>
       </c>
-      <c r="G250" s="7">
+      <c r="G11261" s="7">
         <v>177.56</v>
       </c>
-      <c r="H250" s="7">
+      <c r="H11261" s="7">
         <v>154.21</v>
       </c>
     </row>
     <row r="11262" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A251" s="5" t="s">
+      <c r="A11262" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="B11262" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C251" s="14">
+      <c r="C11262" s="14">
         <v>10003</v>
       </c>
-      <c r="D251" s="5">
+      <c r="D11262" s="5">
         <v>2011</v>
       </c>
-      <c r="E251" s="7">
+      <c r="E11262" s="7">
         <v>-5.54</v>
       </c>
-      <c r="F251" s="7">
+      <c r="F11262" s="7">
         <v>499.23</v>
       </c>
-      <c r="G251" s="7">
+      <c r="G11262" s="7">
         <v>167.73</v>
       </c>
-      <c r="H251" s="7">
+      <c r="H11262" s="7">
         <v>145.66999999999999</v>
       </c>
     </row>
     <row r="11263" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A252" s="5" t="s">
+      <c r="A11263" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B252" s="5" t="s">
+      <c r="B11263" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C252" s="14">
+      <c r="C11263" s="14">
         <v>10003</v>
       </c>
-      <c r="D252" s="5">
+      <c r="D11263" s="5">
         <v>2012</v>
       </c>
-      <c r="E252" s="7">
+      <c r="E11263" s="7">
         <v>-2.78</v>
       </c>
-      <c r="F252" s="7">
+      <c r="F11263" s="7">
         <v>485.33</v>
       </c>
-      <c r="G252" s="7">
+      <c r="G11263" s="7">
         <v>163.06</v>
       </c>
-      <c r="H252" s="7">
+      <c r="H11263" s="7">
         <v>141.61000000000001</v>
       </c>
     </row>
     <row r="11264" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A253" s="5" t="s">
+      <c r="A11264" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B253" s="5" t="s">
+      <c r="B11264" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C253" s="14">
+      <c r="C11264" s="14">
         <v>10003</v>
       </c>
-      <c r="D253" s="5">
+      <c r="D11264" s="5">
         <v>2013</v>
       </c>
-      <c r="E253" s="7">
+      <c r="E11264" s="7">
         <v>1.26</v>
       </c>
-      <c r="F253" s="7">
+      <c r="F11264" s="7">
         <v>491.47</v>
       </c>
-      <c r="G253" s="7">
+      <c r="G11264" s="7">
         <v>165.12</v>
       </c>
-      <c r="H253" s="7">
+      <c r="H11264" s="7">
         <v>143.4</v>
       </c>
     </row>
     <row r="11265" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A254" s="5" t="s">
+      <c r="A11265" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B254" s="5" t="s">
+      <c r="B11265" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C254" s="14">
+      <c r="C11265" s="14">
         <v>10003</v>
       </c>
-      <c r="D254" s="5">
+      <c r="D11265" s="5">
         <v>2014</v>
       </c>
-      <c r="E254" s="7">
+      <c r="E11265" s="7">
         <v>2.56</v>
       </c>
-      <c r="F254" s="7">
+      <c r="F11265" s="7">
         <v>504.05</v>
       </c>
-      <c r="G254" s="7">
+      <c r="G11265" s="7">
         <v>169.35</v>
       </c>
-      <c r="H254" s="7">
+      <c r="H11265" s="7">
         <v>147.07</v>
       </c>
     </row>
     <row r="11266" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A255" s="5" t="s">
+      <c r="A11266" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B255" s="5" t="s">
+      <c r="B11266" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C255" s="14">
+      <c r="C11266" s="14">
         <v>10003</v>
       </c>
-      <c r="D255" s="5">
+      <c r="D11266" s="5">
         <v>2015</v>
       </c>
-      <c r="E255" s="7">
+      <c r="E11266" s="7">
         <v>2.11</v>
       </c>
-      <c r="F255" s="7">
+      <c r="F11266" s="7">
         <v>514.66999999999996</v>
       </c>
-      <c r="G255" s="7">
+      <c r="G11266" s="7">
         <v>172.92</v>
       </c>
-      <c r="H255" s="7">
+      <c r="H11266" s="7">
         <v>150.16999999999999</v>
       </c>
     </row>
     <row r="11267" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A256" s="5" t="s">
+      <c r="A11267" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="B11267" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C256" s="14">
+      <c r="C11267" s="14">
         <v>10003</v>
       </c>
-      <c r="D256" s="5">
+      <c r="D11267" s="5">
         <v>2016</v>
       </c>
-      <c r="E256" s="7">
+      <c r="E11267" s="7">
         <v>1.77</v>
       </c>
-      <c r="F256" s="7">
+      <c r="F11267" s="7">
         <v>523.77</v>
       </c>
-      <c r="G256" s="7">
+      <c r="G11267" s="7">
         <v>175.98</v>
       </c>
-      <c r="H256" s="7">
+      <c r="H11267" s="7">
         <v>152.83000000000001</v>
       </c>
     </row>
     <row r="11268" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A257" s="5" t="s">
+      <c r="A11268" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="B11268" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C257" s="14">
+      <c r="C11268" s="14">
         <v>10003</v>
       </c>
-      <c r="D257" s="5">
+      <c r="D11268" s="5">
         <v>2017</v>
       </c>
-      <c r="E257" s="7">
+      <c r="E11268" s="7">
         <v>1.49</v>
       </c>
-      <c r="F257" s="7">
+      <c r="F11268" s="7">
         <v>531.58000000000004</v>
       </c>
-      <c r="G257" s="7">
+      <c r="G11268" s="7">
         <v>178.6</v>
       </c>
-      <c r="H257" s="7">
+      <c r="H11268" s="7">
         <v>155.1</v>
       </c>
     </row>
     <row r="11269" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A258" s="5" t="s">
+      <c r="A11269" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B258" s="5" t="s">
+      <c r="B11269" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C258" s="14">
+      <c r="C11269" s="14">
         <v>10003</v>
       </c>
-      <c r="D258" s="5">
+      <c r="D11269" s="5">
         <v>2018</v>
       </c>
-      <c r="E258" s="7">
+      <c r="E11269" s="7">
         <v>3.68</v>
       </c>
-      <c r="F258" s="7">
+      <c r="F11269" s="7">
         <v>551.16</v>
       </c>
-      <c r="G258" s="7">
+      <c r="G11269" s="7">
         <v>185.18</v>
       </c>
-      <c r="H258" s="7">
+      <c r="H11269" s="7">
         <v>160.82</v>
       </c>
     </row>
     <row r="11270" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A259" s="5" t="s">
+      <c r="A11270" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B259" s="5" t="s">
+      <c r="B11270" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C259" s="14">
+      <c r="C11270" s="14">
         <v>10003</v>
       </c>
-      <c r="D259" s="5">
+      <c r="D11270" s="5">
         <v>2019</v>
       </c>
-      <c r="E259" s="7">
+      <c r="E11270" s="7">
         <v>3.54</v>
       </c>
-      <c r="F259" s="7">
+      <c r="F11270" s="7">
         <v>570.67999999999995</v>
       </c>
-      <c r="G259" s="7">
+      <c r="G11270" s="7">
         <v>191.73</v>
       </c>
-      <c r="H259" s="7">
+      <c r="H11270" s="7">
         <v>166.51</v>
       </c>
     </row>
     <row r="11271" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A260" s="5" t="s">
+      <c r="A11271" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B260" s="5" t="s">
+      <c r="B11271" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C260" s="14">
+      <c r="C11271" s="14">
         <v>10003</v>
       </c>
-      <c r="D260" s="5">
+      <c r="D11271" s="5">
         <v>2020</v>
       </c>
-      <c r="E260" s="7">
+      <c r="E11271" s="7">
         <v>3.4</v>
       </c>
-      <c r="F260" s="7">
+      <c r="F11271" s="7">
         <v>590.08000000000004</v>
       </c>
-      <c r="G260" s="7">
+      <c r="G11271" s="7">
         <v>198.25</v>
       </c>
-      <c r="H260" s="7">
+      <c r="H11271" s="7">
         <v>172.17</v>
       </c>
     </row>
     <row r="11272" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A261" s="5" t="s">
+      <c r="A11272" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B261" s="5" t="s">
+      <c r="B11272" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C261" s="14">
+      <c r="C11272" s="14">
         <v>10003</v>
       </c>
-      <c r="D261" s="5">
+      <c r="D11272" s="5">
         <v>2021</v>
       </c>
-      <c r="E261" s="7">
+      <c r="E11272" s="7">
         <v>10.26</v>
       </c>
-      <c r="F261" s="7">
+      <c r="F11272" s="7">
         <v>650.63</v>
       </c>
-      <c r="G261" s="7">
+      <c r="G11272" s="7">
         <v>218.6</v>
       </c>
-      <c r="H261" s="7">
+      <c r="H11272" s="7">
         <v>189.84</v>
       </c>
     </row>
     <row r="11273" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A262" s="5" t="s">
+      <c r="A11273" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B262" s="5" t="s">
+      <c r="B11273" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C262" s="14">
+      <c r="C11273" s="14">
         <v>10003</v>
       </c>
-      <c r="D262" s="5">
+      <c r="D11273" s="5">
         <v>2022</v>
       </c>
-      <c r="E262" s="7">
+      <c r="E11273" s="7">
         <v>13.05</v>
       </c>
-      <c r="F262" s="7">
+      <c r="F11273" s="7">
         <v>735.52</v>
       </c>
-      <c r="G262" s="7">
+      <c r="G11273" s="7">
         <v>247.12</v>
       </c>
-      <c r="H262" s="7">
+      <c r="H11273" s="7">
         <v>214.61</v>
       </c>
     </row>
     <row r="11274" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A263" s="5" t="s">
+      <c r="A11274" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B263" s="5" t="s">
+      <c r="B11274" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C263" s="14">
+      <c r="C11274" s="14">
         <v>10003</v>
       </c>
-      <c r="D263" s="5">
+      <c r="D11274" s="5">
         <v>2023</v>
       </c>
-      <c r="E263" s="7">
+      <c r="E11274" s="7">
         <v>9.4600000000000009</v>
       </c>
-      <c r="F263" s="7">
+      <c r="F11274" s="7">
         <v>805.08</v>
       </c>
-      <c r="G263" s="7">
+      <c r="G11274" s="7">
         <v>270.49</v>
       </c>
-      <c r="H263" s="7">
+      <c r="H11274" s="7">
         <v>234.91</v>
       </c>
     </row>
     <row r="11275" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A264" s="5" t="s">
+      <c r="A11275" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B264" s="5" t="s">
+      <c r="B11275" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C264" s="14">
+      <c r="C11275" s="14">
         <v>10003</v>
       </c>
-      <c r="D264" s="5">
+      <c r="D11275" s="5">
         <v>2024</v>
       </c>
-      <c r="E264" s="7">
+      <c r="E11275" s="7">
         <v>6.73</v>
       </c>
-      <c r="F264" s="7">
+      <c r="F11275" s="7">
         <v>859.29</v>
       </c>
-      <c r="G264" s="7">
+      <c r="G11275" s="7">
         <v>288.7</v>
       </c>
-      <c r="H264" s="7">
+      <c r="H11275" s="7">
         <v>250.72</v>
       </c>
     </row>
     <row r="11276" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A265" s="5" t="s">
+      <c r="A11276" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B265" s="5" t="s">
+      <c r="B11276" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="C265" s="14">
+      <c r="C11276" s="14">
         <v>10003</v>
       </c>
-      <c r="D265" s="5">
+      <c r="D11276" s="5">
         <v>2025</v>
       </c>
-      <c r="E265" s="7">
+      <c r="E11276" s="7">
         <v>2.82</v>
       </c>
-      <c r="F265" s="7">
+      <c r="F11276" s="7">
         <v>883.54</v>
       </c>
-      <c r="G265" s="7">
+      <c r="G11276" s="7">
         <v>296.85000000000002</v>
       </c>
-      <c r="H265" s="7">
+      <c r="H11276" s="7">
         <v>257.8</v>
       </c>
     </row>
     <row r="11277" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A266" s="5" t="s">
+      <c r="A11277" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B266" s="5" t="s">
+      <c r="B11277" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C266" s="14">
+      <c r="C11277" s="14">
         <v>10005</v>
       </c>
-      <c r="D266" s="5">
+      <c r="D11277" s="5">
         <v>1983</v>
       </c>
-      <c r="F266" s="7">
+      <c r="F11277" s="7">
         <v>100</v>
       </c>
-      <c r="G266" s="7">
+      <c r="G11277" s="7">
         <v>57.37</v>
       </c>
-      <c r="H266" s="7">
+      <c r="H11277" s="7">
         <v>39.619999999999997</v>
       </c>
     </row>
     <row r="11278" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A267" s="5" t="s">
+      <c r="A11278" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B267" s="5" t="s">
+      <c r="B11278" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C267" s="14">
+      <c r="C11278" s="14">
         <v>10005</v>
       </c>
-      <c r="D267" s="5">
+      <c r="D11278" s="5">
         <v>1984</v>
       </c>
-      <c r="E267" s="7">
+      <c r="E11278" s="7">
         <v>13.74</v>
       </c>
-      <c r="F267" s="7">
+      <c r="F11278" s="7">
         <v>113.74</v>
       </c>
-      <c r="G267" s="7">
+      <c r="G11278" s="7">
         <v>65.25</v>
       </c>
-      <c r="H267" s="7">
+      <c r="H11278" s="7">
         <v>45.06</v>
       </c>
     </row>
     <row r="11279" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A268" s="5" t="s">
+      <c r="A11279" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B268" s="5" t="s">
+      <c r="B11279" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C268" s="14">
+      <c r="C11279" s="14">
         <v>10005</v>
       </c>
-      <c r="D268" s="5">
+      <c r="D11279" s="5">
         <v>1985</v>
       </c>
-      <c r="E268" s="7">
+      <c r="E11279" s="7">
         <v>12.09</v>
       </c>
-      <c r="F268" s="7">
+      <c r="F11279" s="7">
         <v>127.49</v>
       </c>
-      <c r="G268" s="7">
+      <c r="G11279" s="7">
         <v>73.14</v>
       </c>
-      <c r="H268" s="7">
+      <c r="H11279" s="7">
         <v>50.51</v>
       </c>
     </row>
     <row r="11280" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A269" s="5" t="s">
+      <c r="A11280" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="B11280" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C269" s="14">
+      <c r="C11280" s="14">
         <v>10005</v>
       </c>
-      <c r="D269" s="5">
+      <c r="D11280" s="5">
         <v>1986</v>
       </c>
-      <c r="E269" s="7">
+      <c r="E11280" s="7">
         <v>8.44</v>
       </c>
-      <c r="F269" s="7">
+      <c r="F11280" s="7">
         <v>138.25</v>
       </c>
-      <c r="G269" s="7">
+      <c r="G11280" s="7">
         <v>79.31</v>
       </c>
-      <c r="H269" s="7">
+      <c r="H11280" s="7">
         <v>54.77</v>
       </c>
     </row>
     <row r="11281" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A270" s="5" t="s">
+      <c r="A11281" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B11281" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C270" s="14">
+      <c r="C11281" s="14">
         <v>10005</v>
       </c>
-      <c r="D270" s="5">
+      <c r="D11281" s="5">
         <v>1987</v>
       </c>
-      <c r="E270" s="7">
+      <c r="E11281" s="7">
         <v>4.54</v>
       </c>
-      <c r="F270" s="7">
+      <c r="F11281" s="7">
         <v>144.52000000000001</v>
       </c>
-      <c r="G270" s="7">
+      <c r="G11281" s="7">
         <v>82.91</v>
       </c>
-      <c r="H270" s="7">
+      <c r="H11281" s="7">
         <v>57.25</v>
       </c>
     </row>
     <row r="11282" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A271" s="5" t="s">
+      <c r="A11282" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B271" s="5" t="s">
+      <c r="B11282" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C271" s="14">
+      <c r="C11282" s="14">
         <v>10005</v>
       </c>
-      <c r="D271" s="5">
+      <c r="D11282" s="5">
         <v>1988</v>
       </c>
-      <c r="E271" s="7">
+      <c r="E11282" s="7">
         <v>11.38</v>
       </c>
-      <c r="F271" s="7">
+      <c r="F11282" s="7">
         <v>160.96</v>
       </c>
-      <c r="G271" s="7">
+      <c r="G11282" s="7">
         <v>92.35</v>
       </c>
-      <c r="H271" s="7">
+      <c r="H11282" s="7">
         <v>63.77</v>
       </c>
     </row>
     <row r="11283" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A272" s="5" t="s">
+      <c r="A11283" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B272" s="5" t="s">
+      <c r="B11283" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C272" s="14">
+      <c r="C11283" s="14">
         <v>10005</v>
       </c>
-      <c r="D272" s="5">
+      <c r="D11283" s="5">
         <v>1989</v>
       </c>
-      <c r="E272" s="7">
+      <c r="E11283" s="7">
         <v>3.2</v>
       </c>
-      <c r="F272" s="7">
+      <c r="F11283" s="7">
         <v>166.11</v>
       </c>
-      <c r="G272" s="7">
+      <c r="G11283" s="7">
         <v>95.3</v>
       </c>
-      <c r="H272" s="7">
+      <c r="H11283" s="7">
         <v>65.81</v>
       </c>
     </row>
     <row r="11284" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A273" s="5" t="s">
+      <c r="A11284" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B273" s="5" t="s">
+      <c r="B11284" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C273" s="14">
+      <c r="C11284" s="14">
         <v>10005</v>
       </c>
-      <c r="D273" s="5">
+      <c r="D11284" s="5">
         <v>1990</v>
       </c>
-      <c r="E273" s="7">
+      <c r="E11284" s="7">
         <v>4.9400000000000004</v>
       </c>
-      <c r="F273" s="7">
+      <c r="F11284" s="7">
         <v>174.31</v>
       </c>
-      <c r="G273" s="7">
+      <c r="G11284" s="7">
         <v>100</v>
       </c>
-      <c r="H273" s="7">
+      <c r="H11284" s="7">
         <v>69.05</v>
       </c>
     </row>
     <row r="11285" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A274" s="5" t="s">
+      <c r="A11285" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B274" s="5" t="s">
+      <c r="B11285" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C274" s="14">
+      <c r="C11285" s="14">
         <v>10005</v>
       </c>
-      <c r="D274" s="5">
+      <c r="D11285" s="5">
         <v>1991</v>
       </c>
-      <c r="E274" s="7">
+      <c r="E11285" s="7">
         <v>2.89</v>
       </c>
-      <c r="F274" s="7">
+      <c r="F11285" s="7">
         <v>179.35</v>
       </c>
-      <c r="G274" s="7">
+      <c r="G11285" s="7">
         <v>102.89</v>
       </c>
-      <c r="H274" s="7">
+      <c r="H11285" s="7">
         <v>71.05</v>
       </c>
     </row>
     <row r="11286" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A275" s="5" t="s">
+      <c r="A11286" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B275" s="5" t="s">
+      <c r="B11286" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C275" s="14">
+      <c r="C11286" s="14">
         <v>10005</v>
       </c>
-      <c r="D275" s="5">
+      <c r="D11286" s="5">
         <v>1992</v>
       </c>
-      <c r="E275" s="7">
+      <c r="E11286" s="7">
         <v>1.45</v>
       </c>
-      <c r="F275" s="7">
+      <c r="F11286" s="7">
         <v>181.94</v>
       </c>
-      <c r="G275" s="7">
+      <c r="G11286" s="7">
         <v>104.38</v>
       </c>
-      <c r="H275" s="7">
+      <c r="H11286" s="7">
         <v>72.08</v>
       </c>
     </row>
     <row r="11287" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A276" s="5" t="s">
+      <c r="A11287" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B276" s="5" t="s">
+      <c r="B11287" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C276" s="14">
+      <c r="C11287" s="14">
         <v>10005</v>
       </c>
-      <c r="D276" s="5">
+      <c r="D11287" s="5">
         <v>1993</v>
       </c>
-      <c r="E276" s="7">
+      <c r="E11287" s="7">
         <v>0.28999999999999998</v>
       </c>
-      <c r="F276" s="7">
+      <c r="F11287" s="7">
         <v>182.48</v>
       </c>
-      <c r="G276" s="7">
+      <c r="G11287" s="7">
         <v>104.69</v>
       </c>
-      <c r="H276" s="7">
+      <c r="H11287" s="7">
         <v>72.290000000000006</v>
       </c>
     </row>
     <row r="11288" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A277" s="5" t="s">
+      <c r="A11288" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B277" s="5" t="s">
+      <c r="B11288" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C277" s="14">
+      <c r="C11288" s="14">
         <v>10005</v>
       </c>
-      <c r="D277" s="5">
+      <c r="D11288" s="5">
         <v>1994</v>
       </c>
-      <c r="E277" s="7">
+      <c r="E11288" s="7">
         <v>0.13</v>
       </c>
-      <c r="F277" s="7">
+      <c r="F11288" s="7">
         <v>182.72</v>
       </c>
-      <c r="G277" s="7">
+      <c r="G11288" s="7">
         <v>104.82</v>
       </c>
-      <c r="H277" s="7">
+      <c r="H11288" s="7">
         <v>72.39</v>
       </c>
     </row>
     <row r="11289" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A278" s="5" t="s">
+      <c r="A11289" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B278" s="5" t="s">
+      <c r="B11289" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C278" s="14">
+      <c r="C11289" s="14">
         <v>10005</v>
       </c>
-      <c r="D278" s="5">
+      <c r="D11289" s="5">
         <v>1995</v>
       </c>
-      <c r="E278" s="7">
+      <c r="E11289" s="7">
         <v>2.67</v>
       </c>
-      <c r="F278" s="7">
+      <c r="F11289" s="7">
         <v>187.59</v>
       </c>
-      <c r="G278" s="7">
+      <c r="G11289" s="7">
         <v>107.62</v>
       </c>
-      <c r="H278" s="7">
+      <c r="H11289" s="7">
         <v>74.319999999999993</v>
       </c>
     </row>
     <row r="11290" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A279" s="5" t="s">
+      <c r="A11290" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B279" s="5" t="s">
+      <c r="B11290" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C279" s="14">
+      <c r="C11290" s="14">
         <v>10005</v>
       </c>
-      <c r="D279" s="5">
+      <c r="D11290" s="5">
         <v>1996</v>
       </c>
-      <c r="E279" s="7">
+      <c r="E11290" s="7">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F279" s="7">
+      <c r="F11290" s="7">
         <v>195.13</v>
       </c>
-      <c r="G279" s="7">
+      <c r="G11290" s="7">
         <v>111.95</v>
       </c>
-      <c r="H279" s="7">
+      <c r="H11290" s="7">
         <v>77.3</v>
       </c>
     </row>
     <row r="11291" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A280" s="5" t="s">
+      <c r="A11291" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B280" s="5" t="s">
+      <c r="B11291" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C280" s="14">
+      <c r="C11291" s="14">
         <v>10005</v>
       </c>
-      <c r="D280" s="5">
+      <c r="D11291" s="5">
         <v>1997</v>
       </c>
-      <c r="E280" s="7">
+      <c r="E11291" s="7">
         <v>0.31</v>
       </c>
-      <c r="F280" s="7">
+      <c r="F11291" s="7">
         <v>195.74</v>
       </c>
-      <c r="G280" s="7">
+      <c r="G11291" s="7">
         <v>112.3</v>
       </c>
-      <c r="H280" s="7">
+      <c r="H11291" s="7">
         <v>77.55</v>
       </c>
     </row>
     <row r="11292" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A281" s="5" t="s">
+      <c r="A11292" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B281" s="5" t="s">
+      <c r="B11292" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C281" s="14">
+      <c r="C11292" s="14">
         <v>10005</v>
       </c>
-      <c r="D281" s="5">
+      <c r="D11292" s="5">
         <v>1998</v>
       </c>
-      <c r="E281" s="7">
+      <c r="E11292" s="7">
         <v>3.5</v>
       </c>
-      <c r="F281" s="7">
+      <c r="F11292" s="7">
         <v>202.6</v>
       </c>
-      <c r="G281" s="7">
+      <c r="G11292" s="7">
         <v>116.23</v>
       </c>
-      <c r="H281" s="7">
+      <c r="H11292" s="7">
         <v>80.260000000000005</v>
       </c>
     </row>
     <row r="11293" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A282" s="5" t="s">
+      <c r="A11293" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B282" s="5" t="s">
+      <c r="B11293" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C282" s="14">
+      <c r="C11293" s="14">
         <v>10005</v>
       </c>
-      <c r="D282" s="5">
+      <c r="D11293" s="5">
         <v>1999</v>
       </c>
-      <c r="E282" s="7">
+      <c r="E11293" s="7">
         <v>9.3699999999999992</v>
       </c>
-      <c r="F282" s="7">
+      <c r="F11293" s="7">
         <v>221.59</v>
       </c>
-      <c r="G282" s="7">
+      <c r="G11293" s="7">
         <v>127.12</v>
       </c>
-      <c r="H282" s="7">
+      <c r="H11293" s="7">
         <v>87.78</v>
       </c>
     </row>
     <row r="11294" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A283" s="5" t="s">
+      <c r="A11294" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B283" s="5" t="s">
+      <c r="B11294" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C283" s="14">
+      <c r="C11294" s="14">
         <v>10005</v>
       </c>
-      <c r="D283" s="5">
+      <c r="D11294" s="5">
         <v>2000</v>
       </c>
-      <c r="E283" s="7">
+      <c r="E11294" s="7">
         <v>13.92</v>
       </c>
-      <c r="F283" s="7">
+      <c r="F11294" s="7">
         <v>252.42</v>
       </c>
-      <c r="G283" s="7">
+      <c r="G11294" s="7">
         <v>144.82</v>
       </c>
-      <c r="H283" s="7">
+      <c r="H11294" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="11295" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A284" s="5" t="s">
+      <c r="A11295" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B284" s="5" t="s">
+      <c r="B11295" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C284" s="14">
+      <c r="C11295" s="14">
         <v>10005</v>
       </c>
-      <c r="D284" s="5">
+      <c r="D11295" s="5">
         <v>2001</v>
       </c>
-      <c r="E284" s="7">
+      <c r="E11295" s="7">
         <v>12.11</v>
       </c>
-      <c r="F284" s="7">
+      <c r="F11295" s="7">
         <v>282.99</v>
       </c>
-      <c r="G284" s="7">
+      <c r="G11295" s="7">
         <v>162.35</v>
       </c>
-      <c r="H284" s="7">
+      <c r="H11295" s="7">
         <v>112.11</v>
       </c>
     </row>
     <row r="11296" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A285" s="5" t="s">
+      <c r="A11296" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B285" s="5" t="s">
+      <c r="B11296" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C285" s="14">
+      <c r="C11296" s="14">
         <v>10005</v>
       </c>
-      <c r="D285" s="5">
+      <c r="D11296" s="5">
         <v>2002</v>
       </c>
-      <c r="E285" s="7">
+      <c r="E11296" s="7">
         <v>9.24</v>
       </c>
-      <c r="F285" s="7">
+      <c r="F11296" s="7">
         <v>309.14999999999998</v>
       </c>
-      <c r="G285" s="7">
+      <c r="G11296" s="7">
         <v>177.36</v>
       </c>
-      <c r="H285" s="7">
+      <c r="H11296" s="7">
         <v>122.47</v>
       </c>
     </row>
     <row r="11297" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A286" s="5" t="s">
+      <c r="A11297" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B286" s="5" t="s">
+      <c r="B11297" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C286" s="14">
+      <c r="C11297" s="14">
         <v>10005</v>
       </c>
-      <c r="D286" s="5">
+      <c r="D11297" s="5">
         <v>2003</v>
       </c>
-      <c r="E286" s="7">
+      <c r="E11297" s="7">
         <v>9.1199999999999992</v>
       </c>
-      <c r="F286" s="7">
+      <c r="F11297" s="7">
         <v>337.35</v>
       </c>
-      <c r="G286" s="7">
+      <c r="G11297" s="7">
         <v>193.54</v>
       </c>
-      <c r="H286" s="7">
+      <c r="H11297" s="7">
         <v>133.65</v>
       </c>
     </row>
     <row r="11298" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A287" s="5" t="s">
+      <c r="A11298" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B287" s="5" t="s">
+      <c r="B11298" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C287" s="14">
+      <c r="C11298" s="14">
         <v>10005</v>
       </c>
-      <c r="D287" s="5">
+      <c r="D11298" s="5">
         <v>2004</v>
       </c>
-      <c r="E287" s="7">
+      <c r="E11298" s="7">
         <v>17.22</v>
       </c>
-      <c r="F287" s="7">
+      <c r="F11298" s="7">
         <v>395.45</v>
       </c>
-      <c r="G287" s="7">
+      <c r="G11298" s="7">
         <v>226.87</v>
       </c>
-      <c r="H287" s="7">
+      <c r="H11298" s="7">
         <v>156.66</v>
       </c>
     </row>
     <row r="11299" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A288" s="5" t="s">
+      <c r="A11299" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B288" s="5" t="s">
+      <c r="B11299" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C288" s="14">
+      <c r="C11299" s="14">
         <v>10005</v>
       </c>
-      <c r="D288" s="5">
+      <c r="D11299" s="5">
         <v>2005</v>
       </c>
-      <c r="E288" s="7">
+      <c r="E11299" s="7">
         <v>19.36</v>
       </c>
-      <c r="F288" s="7">
+      <c r="F11299" s="7">
         <v>472</v>
       </c>
-      <c r="G288" s="7">
+      <c r="G11299" s="7">
         <v>270.79000000000002</v>
       </c>
-      <c r="H288" s="7">
+      <c r="H11299" s="7">
         <v>186.99</v>
       </c>
     </row>
     <row r="11300" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A289" s="5" t="s">
+      <c r="A11300" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B289" s="5" t="s">
+      <c r="B11300" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C289" s="14">
+      <c r="C11300" s="14">
         <v>10005</v>
       </c>
-      <c r="D289" s="5">
+      <c r="D11300" s="5">
         <v>2006</v>
       </c>
-      <c r="E289" s="7">
+      <c r="E11300" s="7">
         <v>9.4499999999999993</v>
       </c>
-      <c r="F289" s="7">
+      <c r="F11300" s="7">
         <v>516.62</v>
       </c>
-      <c r="G289" s="7">
+      <c r="G11300" s="7">
         <v>296.39</v>
       </c>
-      <c r="H289" s="7">
+      <c r="H11300" s="7">
         <v>204.66</v>
       </c>
     </row>
     <row r="11301" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A290" s="5" t="s">
+      <c r="A11301" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B290" s="5" t="s">
+      <c r="B11301" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C290" s="14">
+      <c r="C11301" s="14">
         <v>10005</v>
       </c>
-      <c r="D290" s="5">
+      <c r="D11301" s="5">
         <v>2007</v>
       </c>
-      <c r="E290" s="7">
+      <c r="E11301" s="7">
         <v>1.1399999999999999</v>
       </c>
-      <c r="F290" s="7">
+      <c r="F11301" s="7">
         <v>522.51</v>
       </c>
-      <c r="G290" s="7">
+      <c r="G11301" s="7">
         <v>299.77</v>
       </c>
-      <c r="H290" s="7">
+      <c r="H11301" s="7">
         <v>207</v>
       </c>
     </row>
     <row r="11302" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A291" s="5" t="s">
+      <c r="A11302" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B291" s="5" t="s">
+      <c r="B11302" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C291" s="14">
+      <c r="C11302" s="14">
         <v>10005</v>
       </c>
-      <c r="D291" s="5">
+      <c r="D11302" s="5">
         <v>2008</v>
       </c>
-      <c r="E291" s="7">
+      <c r="E11302" s="7">
         <v>-3.45</v>
       </c>
-      <c r="F291" s="7">
+      <c r="F11302" s="7">
         <v>504.48</v>
       </c>
-      <c r="G291" s="7">
+      <c r="G11302" s="7">
         <v>289.42</v>
       </c>
-      <c r="H291" s="7">
+      <c r="H11302" s="7">
         <v>199.86</v>
       </c>
     </row>
     <row r="11303" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A292" s="5" t="s">
+      <c r="A11303" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B292" s="5" t="s">
+      <c r="B11303" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C292" s="14">
+      <c r="C11303" s="14">
         <v>10005</v>
       </c>
-      <c r="D292" s="5">
+      <c r="D11303" s="5">
         <v>2009</v>
       </c>
-      <c r="E292" s="7">
+      <c r="E11303" s="7">
         <v>-7.25</v>
       </c>
-      <c r="F292" s="7">
+      <c r="F11303" s="7">
         <v>467.91</v>
       </c>
-      <c r="G292" s="7">
+      <c r="G11303" s="7">
         <v>268.44</v>
       </c>
-      <c r="H292" s="7">
+      <c r="H11303" s="7">
         <v>185.37</v>
       </c>
     </row>
     <row r="11304" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A293" s="5" t="s">
+      <c r="A11304" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B293" s="5" t="s">
+      <c r="B11304" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C293" s="14">
+      <c r="C11304" s="14">
         <v>10005</v>
       </c>
-      <c r="D293" s="5">
+      <c r="D11304" s="5">
         <v>2010</v>
       </c>
-      <c r="E293" s="7">
+      <c r="E11304" s="7">
         <v>-5.77</v>
       </c>
-      <c r="F293" s="7">
+      <c r="F11304" s="7">
         <v>440.92</v>
       </c>
-      <c r="G293" s="7">
+      <c r="G11304" s="7">
         <v>252.95</v>
       </c>
-      <c r="H293" s="7">
+      <c r="H11304" s="7">
         <v>174.67</v>
       </c>
     </row>
     <row r="11305" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A294" s="5" t="s">
+      <c r="A11305" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B294" s="5" t="s">
+      <c r="B11305" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C294" s="14">
+      <c r="C11305" s="14">
         <v>10005</v>
       </c>
-      <c r="D294" s="5">
+      <c r="D11305" s="5">
         <v>2011</v>
       </c>
-      <c r="E294" s="7">
+      <c r="E11305" s="7">
         <v>-5.8</v>
       </c>
-      <c r="F294" s="7">
+      <c r="F11305" s="7">
         <v>415.36</v>
       </c>
-      <c r="G294" s="7">
+      <c r="G11305" s="7">
         <v>238.29</v>
       </c>
-      <c r="H294" s="7">
+      <c r="H11305" s="7">
         <v>164.55</v>
       </c>
     </row>
     <row r="11306" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A295" s="5" t="s">
+      <c r="A11306" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B295" s="5" t="s">
+      <c r="B11306" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C295" s="14">
+      <c r="C11306" s="14">
         <v>10005</v>
       </c>
-      <c r="D295" s="5">
+      <c r="D11306" s="5">
         <v>2012</v>
       </c>
-      <c r="E295" s="7">
+      <c r="E11306" s="7">
         <v>-2.54</v>
       </c>
-      <c r="F295" s="7">
+      <c r="F11306" s="7">
         <v>404.79</v>
       </c>
-      <c r="G295" s="7">
+      <c r="G11306" s="7">
         <v>232.23</v>
       </c>
-      <c r="H295" s="7">
+      <c r="H11306" s="7">
         <v>160.36000000000001</v>
       </c>
     </row>
     <row r="11307" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A296" s="5" t="s">
+      <c r="A11307" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B296" s="5" t="s">
+      <c r="B11307" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C296" s="14">
+      <c r="C11307" s="14">
         <v>10005</v>
       </c>
-      <c r="D296" s="5">
+      <c r="D11307" s="5">
         <v>2013</v>
       </c>
-      <c r="E296" s="7">
+      <c r="E11307" s="7">
         <v>-1.02</v>
       </c>
-      <c r="F296" s="7">
+      <c r="F11307" s="7">
         <v>400.66</v>
       </c>
-      <c r="G296" s="7">
+      <c r="G11307" s="7">
         <v>229.86</v>
       </c>
-      <c r="H296" s="7">
+      <c r="H11307" s="7">
         <v>158.72999999999999</v>
       </c>
     </row>
     <row r="11308" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A297" s="5" t="s">
+      <c r="A11308" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B297" s="5" t="s">
+      <c r="B11308" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C297" s="14">
+      <c r="C11308" s="14">
         <v>10005</v>
       </c>
-      <c r="D297" s="5">
+      <c r="D11308" s="5">
         <v>2014</v>
       </c>
-      <c r="E297" s="7">
+      <c r="E11308" s="7">
         <v>1.91</v>
       </c>
-      <c r="F297" s="7">
+      <c r="F11308" s="7">
         <v>408.3</v>
       </c>
-      <c r="G297" s="7">
+      <c r="G11308" s="7">
         <v>234.25</v>
       </c>
-      <c r="H297" s="7">
+      <c r="H11308" s="7">
         <v>161.75</v>
       </c>
     </row>
     <row r="11309" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A298" s="5" t="s">
+      <c r="A11309" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B298" s="5" t="s">
+      <c r="B11309" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C298" s="14">
+      <c r="C11309" s="14">
         <v>10005</v>
       </c>
-      <c r="D298" s="5">
+      <c r="D11309" s="5">
         <v>2015</v>
       </c>
-      <c r="E298" s="7">
+      <c r="E11309" s="7">
         <v>2.5499999999999998</v>
       </c>
-      <c r="F298" s="7">
+      <c r="F11309" s="7">
         <v>418.7</v>
       </c>
-      <c r="G298" s="7">
+      <c r="G11309" s="7">
         <v>240.21</v>
       </c>
-      <c r="H298" s="7">
+      <c r="H11309" s="7">
         <v>165.87</v>
       </c>
     </row>
     <row r="11310" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A299" s="5" t="s">
+      <c r="A11310" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B299" s="5" t="s">
+      <c r="B11310" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C299" s="14">
+      <c r="C11310" s="14">
         <v>10005</v>
       </c>
-      <c r="D299" s="5">
+      <c r="D11310" s="5">
         <v>2016</v>
       </c>
-      <c r="E299" s="7">
+      <c r="E11310" s="7">
         <v>2.0299999999999998</v>
       </c>
-      <c r="F299" s="7">
+      <c r="F11310" s="7">
         <v>427.19</v>
       </c>
-      <c r="G299" s="7">
+      <c r="G11310" s="7">
         <v>245.08</v>
       </c>
-      <c r="H299" s="7">
+      <c r="H11310" s="7">
         <v>169.24</v>
       </c>
     </row>
     <row r="11311" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A300" s="5" t="s">
+      <c r="A11311" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B300" s="5" t="s">
+      <c r="B11311" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C300" s="14">
+      <c r="C11311" s="14">
         <v>10005</v>
       </c>
-      <c r="D300" s="5">
+      <c r="D11311" s="5">
         <v>2017</v>
       </c>
-      <c r="E300" s="7">
+      <c r="E11311" s="7">
         <v>3.7</v>
       </c>
-      <c r="F300" s="7">
+      <c r="F11311" s="7">
         <v>443</v>
       </c>
-      <c r="G300" s="7">
+      <c r="G11311" s="7">
         <v>254.15</v>
       </c>
-      <c r="H300" s="7">
+      <c r="H11311" s="7">
         <v>175.5</v>
       </c>
     </row>
     <row r="11312" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A301" s="5" t="s">
+      <c r="A11312" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B301" s="5" t="s">
+      <c r="B11312" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C301" s="14">
+      <c r="C11312" s="14">
         <v>10005</v>
       </c>
-      <c r="D301" s="5">
+      <c r="D11312" s="5">
         <v>2018</v>
       </c>
-      <c r="E301" s="7">
+      <c r="E11312" s="7">
         <v>3.83</v>
       </c>
-      <c r="F301" s="7">
+      <c r="F11312" s="7">
         <v>459.97</v>
       </c>
-      <c r="G301" s="7">
+      <c r="G11312" s="7">
         <v>263.89</v>
       </c>
-      <c r="H301" s="7">
+      <c r="H11312" s="7">
         <v>182.22</v>
       </c>
     </row>
     <row r="11313" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A302" s="5" t="s">
+      <c r="A11313" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B302" s="5" t="s">
+      <c r="B11313" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C302" s="14">
+      <c r="C11313" s="14">
         <v>10005</v>
       </c>
-      <c r="D302" s="5">
+      <c r="D11313" s="5">
         <v>2019</v>
       </c>
-      <c r="E302" s="7">
+      <c r="E11313" s="7">
         <v>4.74</v>
       </c>
-      <c r="F302" s="7">
+      <c r="F11313" s="7">
         <v>481.78</v>
       </c>
-      <c r="G302" s="7">
+      <c r="G11313" s="7">
         <v>276.39999999999998</v>
       </c>
-      <c r="H302" s="7">
+      <c r="H11313" s="7">
         <v>190.86</v>
       </c>
     </row>
     <row r="11314" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A303" s="5" t="s">
+      <c r="A11314" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B303" s="5" t="s">
+      <c r="B11314" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C303" s="14">
+      <c r="C11314" s="14">
         <v>10005</v>
       </c>
-      <c r="D303" s="5">
+      <c r="D11314" s="5">
         <v>2020</v>
       </c>
-      <c r="E303" s="7">
+      <c r="E11314" s="7">
         <v>2.5299999999999998</v>
       </c>
-      <c r="F303" s="7">
+      <c r="F11314" s="7">
         <v>493.99</v>
       </c>
-      <c r="G303" s="7">
+      <c r="G11314" s="7">
         <v>283.39999999999998</v>
       </c>
-      <c r="H303" s="7">
+      <c r="H11314" s="7">
         <v>195.7</v>
       </c>
     </row>
     <row r="11315" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A304" s="5" t="s">
+      <c r="A11315" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B304" s="5" t="s">
+      <c r="B11315" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C304" s="14">
+      <c r="C11315" s="14">
         <v>10005</v>
       </c>
-      <c r="D304" s="5">
+      <c r="D11315" s="5">
         <v>2021</v>
       </c>
-      <c r="E304" s="7">
+      <c r="E11315" s="7">
         <v>12.07</v>
       </c>
-      <c r="F304" s="7">
+      <c r="F11315" s="7">
         <v>553.62</v>
       </c>
-      <c r="G304" s="7">
+      <c r="G11315" s="7">
         <v>317.61</v>
       </c>
-      <c r="H304" s="7">
+      <c r="H11315" s="7">
         <v>219.32</v>
       </c>
     </row>
     <row r="11316" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A305" s="5" t="s">
+      <c r="A11316" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B305" s="5" t="s">
+      <c r="B11316" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C305" s="14">
+      <c r="C11316" s="14">
         <v>10005</v>
       </c>
-      <c r="D305" s="5">
+      <c r="D11316" s="5">
         <v>2022</v>
       </c>
-      <c r="E305" s="7">
+      <c r="E11316" s="7">
         <v>16.66</v>
       </c>
-      <c r="F305" s="7">
+      <c r="F11316" s="7">
         <v>645.84</v>
       </c>
-      <c r="G305" s="7">
+      <c r="G11316" s="7">
         <v>370.52</v>
       </c>
-      <c r="H305" s="7">
+      <c r="H11316" s="7">
         <v>255.86</v>
       </c>
     </row>
     <row r="11317" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A306" s="5" t="s">
+      <c r="A11317" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B306" s="5" t="s">
+      <c r="B11317" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C306" s="14">
+      <c r="C11317" s="14">
         <v>10005</v>
       </c>
-      <c r="D306" s="5">
+      <c r="D11317" s="5">
         <v>2023</v>
       </c>
-      <c r="E306" s="7">
+      <c r="E11317" s="7">
         <v>5.18</v>
       </c>
-      <c r="F306" s="7">
+      <c r="F11317" s="7">
         <v>679.28</v>
       </c>
-      <c r="G306" s="7">
+      <c r="G11317" s="7">
         <v>389.71</v>
       </c>
-      <c r="H306" s="7">
+      <c r="H11317" s="7">
         <v>269.11</v>
       </c>
     </row>
     <row r="11318" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A307" s="5" t="s">
+      <c r="A11318" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B307" s="5" t="s">
+      <c r="B11318" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C307" s="14">
+      <c r="C11318" s="14">
         <v>10005</v>
       </c>
-      <c r="D307" s="5">
+      <c r="D11318" s="5">
         <v>2024</v>
       </c>
-      <c r="E307" s="7">
+      <c r="E11318" s="7">
         <v>8.34</v>
       </c>
-      <c r="F307" s="7">
+      <c r="F11318" s="7">
         <v>735.91</v>
       </c>
-      <c r="G307" s="7">
+      <c r="G11318" s="7">
         <v>422.19</v>
       </c>
-      <c r="H307" s="7">
+      <c r="H11318" s="7">
         <v>291.54000000000002</v>
       </c>
     </row>
     <row r="11319" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A308" s="5" t="s">
+      <c r="A11319" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B308" s="5" t="s">
+      <c r="B11319" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="C308" s="14">
+      <c r="C11319" s="14">
         <v>10005</v>
       </c>
-      <c r="D308" s="5">
+      <c r="D11319" s="5">
         <v>2025</v>
       </c>
-      <c r="E308" s="7">
+      <c r="E11319" s="7">
         <v>5.34</v>
       </c>
-      <c r="F308" s="7">
+      <c r="F11319" s="7">
         <v>775.2</v>
       </c>
-      <c r="G308" s="7">
+      <c r="G11319" s="7">
         <v>444.74</v>
       </c>
-      <c r="H308" s="7">
+      <c r="H11319" s="7">
         <v>307.11</v>
       </c>
     </row>
